--- a/BKQBF_TAB-8.xlsx
+++ b/BKQBF_TAB-8.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/BK_Compra_Perfeita/CPerfect_Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/BK_Compra_Perfeita/CPerfect_Files_GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{DD6C80B2-8265-445B-9730-F2D404ECD668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DDD1127-93DD-4E4D-B76B-391488D1D5B8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC2B3CF5-1FCC-4681-9DE1-AA91DC589256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{53633E7E-D6F2-4DB1-8EFC-B5ACF3C598DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Estoque" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Estoque!$F$1:$I$169</definedName>
-  </definedNames>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="173">
   <si>
     <t>DESCRIÇÃO</t>
   </si>
@@ -554,7 +556,10 @@
     <t>var1semana</t>
   </si>
   <si>
-    <t>NA</t>
+    <t>ATU 17AGO</t>
+  </si>
+  <si>
+    <t>ATU25AGO</t>
   </si>
 </sst>
 </file>
@@ -586,7 +591,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -602,12 +607,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,7 +651,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -679,7 +678,6 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,6 +693,1915 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="CONTAGEM_DIARIA_JUL25"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>Contagem DIARIA de Estoque  | BK Sorocaba Shopping | 26487</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>DATA:</v>
+          </cell>
+          <cell r="C4">
+            <v>45886</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>RESPONSÁVEL  DIU:</v>
+          </cell>
+          <cell r="J4" t="str">
+            <v>RESPONSÁVEL  NOT:</v>
+          </cell>
+          <cell r="L4" t="str">
+            <v>flavia</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>CÓD</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>DESCRIÇÃO</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>CONTAGEM  ABERTURA  (até 10h00)</v>
+          </cell>
+          <cell r="H5" t="str">
+            <v>RECEBIMENTO</v>
+          </cell>
+          <cell r="J5" t="str">
+            <v>CONTAGEM  FECHAMENTO  (após 22h00)</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="D6" t="str">
+            <v>CAIXA</v>
+          </cell>
+          <cell r="E6" t="str">
+            <v>PC ou FD</v>
+          </cell>
+          <cell r="F6" t="str">
+            <v>KG ou UND</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v>TOTAL</v>
+          </cell>
+          <cell r="H6" t="str">
+            <v>CAIXA</v>
+          </cell>
+          <cell r="I6" t="str">
+            <v>TOTAL</v>
+          </cell>
+          <cell r="J6" t="str">
+            <v>CAIXA</v>
+          </cell>
+          <cell r="K6" t="str">
+            <v>PC ou FD</v>
+          </cell>
+          <cell r="L6" t="str">
+            <v>KG ou UND</v>
+          </cell>
+          <cell r="M6" t="str">
+            <v>TOTAL</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>21403</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>CARNE CONG MOIDA WHOPPER - 152UN</v>
+          </cell>
+          <cell r="G7">
+            <v>0</v>
+          </cell>
+          <cell r="I7">
+            <v>0</v>
+          </cell>
+          <cell r="J7">
+            <v>3</v>
+          </cell>
+          <cell r="M7">
+            <v>456</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8">
+            <v>35622</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>CARNE HB MOIDA CONGELADA 2.0 - 333UN</v>
+          </cell>
+          <cell r="G8">
+            <v>0</v>
+          </cell>
+          <cell r="I8">
+            <v>0</v>
+          </cell>
+          <cell r="J8">
+            <v>3</v>
+          </cell>
+          <cell r="L8">
+            <v>62</v>
+          </cell>
+          <cell r="M8">
+            <v>1061</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9">
+            <v>38178</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>HAMBURGUER BASE DE VEGETAIS 2.0 - 122UN</v>
+          </cell>
+          <cell r="G9">
+            <v>0</v>
+          </cell>
+          <cell r="I9">
+            <v>0</v>
+          </cell>
+          <cell r="M9">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>34580</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>BK CHICKEN - 588UN</v>
+          </cell>
+          <cell r="G10">
+            <v>0</v>
+          </cell>
+          <cell r="I10">
+            <v>0</v>
+          </cell>
+          <cell r="K10">
+            <v>7</v>
+          </cell>
+          <cell r="L10">
+            <v>17</v>
+          </cell>
+          <cell r="M10">
+            <v>360</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>36204</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>CHICKEN JR - 152UN</v>
+          </cell>
+          <cell r="G11">
+            <v>0</v>
+          </cell>
+          <cell r="I11">
+            <v>0</v>
+          </cell>
+          <cell r="J11">
+            <v>1</v>
+          </cell>
+          <cell r="K11">
+            <v>2</v>
+          </cell>
+          <cell r="L11">
+            <v>14</v>
+          </cell>
+          <cell r="M11">
+            <v>204</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12">
+            <v>36206</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>TENDER CRISPY FILE - 72UN</v>
+          </cell>
+          <cell r="G12">
+            <v>0</v>
+          </cell>
+          <cell r="I12">
+            <v>0</v>
+          </cell>
+          <cell r="K12">
+            <v>2</v>
+          </cell>
+          <cell r="L12">
+            <v>3</v>
+          </cell>
+          <cell r="M12">
+            <v>39</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>35103</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>PAO HB CONG HAMBURGUER - 270UN</v>
+          </cell>
+          <cell r="G13">
+            <v>0</v>
+          </cell>
+          <cell r="I13">
+            <v>0</v>
+          </cell>
+          <cell r="J13">
+            <v>2</v>
+          </cell>
+          <cell r="K13">
+            <v>21</v>
+          </cell>
+          <cell r="L13">
+            <v>27</v>
+          </cell>
+          <cell r="M13">
+            <v>1197</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14">
+            <v>38585</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>PAO BRIOCHE - 192UN</v>
+          </cell>
+          <cell r="G14">
+            <v>0</v>
+          </cell>
+          <cell r="I14">
+            <v>0</v>
+          </cell>
+          <cell r="K14">
+            <v>4</v>
+          </cell>
+          <cell r="L14">
+            <v>16</v>
+          </cell>
+          <cell r="M14">
+            <v>80</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15">
+            <v>36252</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>PAO SUPREMO - 180UN</v>
+          </cell>
+          <cell r="G15">
+            <v>0</v>
+          </cell>
+          <cell r="I15">
+            <v>0</v>
+          </cell>
+          <cell r="J15">
+            <v>1</v>
+          </cell>
+          <cell r="K15">
+            <v>11</v>
+          </cell>
+          <cell r="M15">
+            <v>345</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>34754</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>PAO WHOPPER - 120UN</v>
+          </cell>
+          <cell r="G16">
+            <v>0</v>
+          </cell>
+          <cell r="I16">
+            <v>0</v>
+          </cell>
+          <cell r="J16">
+            <v>1</v>
+          </cell>
+          <cell r="K16">
+            <v>12</v>
+          </cell>
+          <cell r="L16">
+            <v>15</v>
+          </cell>
+          <cell r="M16">
+            <v>375</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17">
+            <v>35619</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>QUEIJO CHEDDAR - 1536UN</v>
+          </cell>
+          <cell r="G17">
+            <v>0</v>
+          </cell>
+          <cell r="I17">
+            <v>0</v>
+          </cell>
+          <cell r="J17">
+            <v>1</v>
+          </cell>
+          <cell r="K17">
+            <v>4</v>
+          </cell>
+          <cell r="M17">
+            <v>2304</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18">
+            <v>21055</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>BATATA CONGELADA - 12,5K</v>
+          </cell>
+          <cell r="G18">
+            <v>0</v>
+          </cell>
+          <cell r="I18">
+            <v>0</v>
+          </cell>
+          <cell r="J18">
+            <v>6</v>
+          </cell>
+          <cell r="K18">
+            <v>4</v>
+          </cell>
+          <cell r="L18">
+            <v>1.98</v>
+          </cell>
+          <cell r="M18">
+            <v>86.98</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19">
+            <v>34298</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>BROWNIE BRIGADEIRO - 24UN</v>
+          </cell>
+          <cell r="G19">
+            <v>0</v>
+          </cell>
+          <cell r="I19">
+            <v>0</v>
+          </cell>
+          <cell r="J19">
+            <v>1</v>
+          </cell>
+          <cell r="L19">
+            <v>1</v>
+          </cell>
+          <cell r="M19">
+            <v>25</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20">
+            <v>39142</v>
+          </cell>
+          <cell r="C20" t="str">
+            <v>LEITE EM PÓ NINHO - 6,9KG</v>
+          </cell>
+          <cell r="G20">
+            <v>0</v>
+          </cell>
+          <cell r="I20">
+            <v>0</v>
+          </cell>
+          <cell r="K20">
+            <v>3</v>
+          </cell>
+          <cell r="M20">
+            <v>1.7249999999999999</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21">
+            <v>39679</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>BRINDE BRINQUEDOS</v>
+          </cell>
+          <cell r="G21">
+            <v>0</v>
+          </cell>
+          <cell r="I21">
+            <v>0</v>
+          </cell>
+          <cell r="M21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22">
+            <v>39060</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v xml:space="preserve">BRINDE COPO </v>
+          </cell>
+          <cell r="G22">
+            <v>0</v>
+          </cell>
+          <cell r="I22">
+            <v>0</v>
+          </cell>
+          <cell r="M22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23">
+            <v>8791</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>ÁGUA GASEIFICADA H20 - 12UN</v>
+          </cell>
+          <cell r="G23">
+            <v>0</v>
+          </cell>
+          <cell r="I23">
+            <v>0</v>
+          </cell>
+          <cell r="M23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24">
+            <v>9085</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>GUARANA ANTARCTICA DIET LATA - 12UN</v>
+          </cell>
+          <cell r="G24">
+            <v>0</v>
+          </cell>
+          <cell r="I24">
+            <v>0</v>
+          </cell>
+          <cell r="M24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25">
+            <v>9084</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>GUARANA ANTARCTICA LATA - 12UN</v>
+          </cell>
+          <cell r="G25">
+            <v>0</v>
+          </cell>
+          <cell r="I25">
+            <v>0</v>
+          </cell>
+          <cell r="M25">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26">
+            <v>9096</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>PEPSI COLA LATA - 12UN</v>
+          </cell>
+          <cell r="G26">
+            <v>0</v>
+          </cell>
+          <cell r="I26">
+            <v>0</v>
+          </cell>
+          <cell r="M26">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27">
+            <v>9274</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>PEPSI ZERO LATA - 12UN</v>
+          </cell>
+          <cell r="G27">
+            <v>0</v>
+          </cell>
+          <cell r="I27">
+            <v>0</v>
+          </cell>
+          <cell r="M27">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28">
+            <v>35047</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>SUCO DE MARACUJA - 12UN</v>
+          </cell>
+          <cell r="G28">
+            <v>0</v>
+          </cell>
+          <cell r="I28">
+            <v>0</v>
+          </cell>
+          <cell r="M28">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29">
+            <v>35959</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>SUCO LARANJA - 12UN</v>
+          </cell>
+          <cell r="G29">
+            <v>0</v>
+          </cell>
+          <cell r="I29">
+            <v>0</v>
+          </cell>
+          <cell r="M29">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30">
+            <v>35046</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>SUCO UVA - 12UN</v>
+          </cell>
+          <cell r="G30">
+            <v>0</v>
+          </cell>
+          <cell r="I30">
+            <v>0</v>
+          </cell>
+          <cell r="M30">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31">
+            <v>10143</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>CHA LIPTON LIMAO - 12UN</v>
+          </cell>
+          <cell r="G31">
+            <v>0</v>
+          </cell>
+          <cell r="I31">
+            <v>0</v>
+          </cell>
+          <cell r="M31">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32">
+            <v>10141</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>CHA LIPTON PESSEGO - 12UN</v>
+          </cell>
+          <cell r="G32">
+            <v>0</v>
+          </cell>
+          <cell r="I32">
+            <v>0</v>
+          </cell>
+          <cell r="M32">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Plan_PEDIDO_out24"/>
+      <sheetName val="ENTREGA_26ago"/>
+      <sheetName val="CONTAGEM_DIARIA_JUL25"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>Contagem DIARIA de Estoque  | BK Sorocaba Shopping | 26487</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>DATA:</v>
+          </cell>
+          <cell r="C4">
+            <v>45894</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>RESPONSÁVEL  DIU:</v>
+          </cell>
+          <cell r="J4" t="str">
+            <v>RESPONSÁVEL  NOT:</v>
+          </cell>
+          <cell r="L4" t="str">
+            <v>flavia</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>CÓD</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>DESCRIÇÃO</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>CONTAGEM  ABERTURA  (até 10h00)</v>
+          </cell>
+          <cell r="H5" t="str">
+            <v>RECEBIMENTO</v>
+          </cell>
+          <cell r="J5" t="str">
+            <v>CONTAGEM  FECHAMENTO  (após 22h00)</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="D6" t="str">
+            <v>CAIXA</v>
+          </cell>
+          <cell r="E6" t="str">
+            <v>PC ou FD</v>
+          </cell>
+          <cell r="F6" t="str">
+            <v>KG ou UND</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v>TOTAL</v>
+          </cell>
+          <cell r="H6" t="str">
+            <v>CAIXA</v>
+          </cell>
+          <cell r="I6" t="str">
+            <v>TOTAL</v>
+          </cell>
+          <cell r="J6" t="str">
+            <v>CAIXA</v>
+          </cell>
+          <cell r="K6" t="str">
+            <v>PC ou FD</v>
+          </cell>
+          <cell r="L6" t="str">
+            <v>KG ou UND</v>
+          </cell>
+          <cell r="M6" t="str">
+            <v>TOTAL</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>21403</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>CARNE CONG MOIDA WHOPPER - 152UN</v>
+          </cell>
+          <cell r="G7">
+            <v>0</v>
+          </cell>
+          <cell r="I7">
+            <v>0</v>
+          </cell>
+          <cell r="L7">
+            <v>26</v>
+          </cell>
+          <cell r="M7">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8">
+            <v>36409</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>CARNE HB MOIDA CONGELADA 2.0 - 333UN</v>
+          </cell>
+          <cell r="G8">
+            <v>0</v>
+          </cell>
+          <cell r="I8">
+            <v>0</v>
+          </cell>
+          <cell r="J8">
+            <v>2</v>
+          </cell>
+          <cell r="L8">
+            <v>159</v>
+          </cell>
+          <cell r="M8">
+            <v>825</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9">
+            <v>38178</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>HAMBURGUER BASE DE VEGETAIS 2.0 - 122UN</v>
+          </cell>
+          <cell r="G9">
+            <v>0</v>
+          </cell>
+          <cell r="I9">
+            <v>0</v>
+          </cell>
+          <cell r="L9">
+            <v>77</v>
+          </cell>
+          <cell r="M9">
+            <v>77</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>34580</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>BK CHICKEN - 588UN</v>
+          </cell>
+          <cell r="G10">
+            <v>0</v>
+          </cell>
+          <cell r="I10">
+            <v>0</v>
+          </cell>
+          <cell r="K10">
+            <v>1</v>
+          </cell>
+          <cell r="L10">
+            <v>22</v>
+          </cell>
+          <cell r="M10">
+            <v>71</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>31777</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>CHICKEN JR - 152UN</v>
+          </cell>
+          <cell r="G11">
+            <v>0</v>
+          </cell>
+          <cell r="I11">
+            <v>0</v>
+          </cell>
+          <cell r="L11">
+            <v>12</v>
+          </cell>
+          <cell r="M11">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12">
+            <v>36206</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>TENDER CRISPY FILE - 72UN</v>
+          </cell>
+          <cell r="G12">
+            <v>0</v>
+          </cell>
+          <cell r="I12">
+            <v>0</v>
+          </cell>
+          <cell r="K12">
+            <v>1</v>
+          </cell>
+          <cell r="L12">
+            <v>7</v>
+          </cell>
+          <cell r="M12">
+            <v>25</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>34840</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>PAO HB CONG HAMBURGUER - 270UN</v>
+          </cell>
+          <cell r="G13">
+            <v>0</v>
+          </cell>
+          <cell r="I13">
+            <v>0</v>
+          </cell>
+          <cell r="J13">
+            <v>1</v>
+          </cell>
+          <cell r="K13">
+            <v>9</v>
+          </cell>
+          <cell r="L13">
+            <v>6</v>
+          </cell>
+          <cell r="M13">
+            <v>546</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14">
+            <v>38585</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>PAO BRIOCHE - 192UN</v>
+          </cell>
+          <cell r="G14">
+            <v>0</v>
+          </cell>
+          <cell r="I14">
+            <v>0</v>
+          </cell>
+          <cell r="K14">
+            <v>4</v>
+          </cell>
+          <cell r="L14">
+            <v>19</v>
+          </cell>
+          <cell r="M14">
+            <v>83</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15">
+            <v>36252</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>PAO SUPREMO - 180UN</v>
+          </cell>
+          <cell r="G15">
+            <v>0</v>
+          </cell>
+          <cell r="I15">
+            <v>0</v>
+          </cell>
+          <cell r="K15">
+            <v>12</v>
+          </cell>
+          <cell r="L15">
+            <v>14</v>
+          </cell>
+          <cell r="M15">
+            <v>194</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>34754</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>PAO WHOPPER - 120UN</v>
+          </cell>
+          <cell r="G16">
+            <v>0</v>
+          </cell>
+          <cell r="I16">
+            <v>0</v>
+          </cell>
+          <cell r="K16">
+            <v>7</v>
+          </cell>
+          <cell r="L16">
+            <v>19</v>
+          </cell>
+          <cell r="M16">
+            <v>159</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17">
+            <v>35610</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>QUEIJO CHEDDAR - 1536UN</v>
+          </cell>
+          <cell r="G17">
+            <v>0</v>
+          </cell>
+          <cell r="I17">
+            <v>0</v>
+          </cell>
+          <cell r="J17">
+            <v>1</v>
+          </cell>
+          <cell r="K17">
+            <v>1</v>
+          </cell>
+          <cell r="L17">
+            <v>96</v>
+          </cell>
+          <cell r="M17">
+            <v>1824</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18">
+            <v>21055</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>BATATA CONGELADA - 12,5K</v>
+          </cell>
+          <cell r="G18">
+            <v>0</v>
+          </cell>
+          <cell r="I18">
+            <v>0</v>
+          </cell>
+          <cell r="J18">
+            <v>2</v>
+          </cell>
+          <cell r="L18">
+            <v>0.308</v>
+          </cell>
+          <cell r="M18">
+            <v>25.308</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19">
+            <v>34298</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>BROWNIE BRIGADEIRO - 24UN</v>
+          </cell>
+          <cell r="G19">
+            <v>0</v>
+          </cell>
+          <cell r="I19">
+            <v>0</v>
+          </cell>
+          <cell r="L19">
+            <v>17</v>
+          </cell>
+          <cell r="M19">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20">
+            <v>39142</v>
+          </cell>
+          <cell r="C20" t="str">
+            <v>LEITE EM PÓ NINHO - 6,9KG</v>
+          </cell>
+          <cell r="G20">
+            <v>0</v>
+          </cell>
+          <cell r="I20">
+            <v>0</v>
+          </cell>
+          <cell r="K20">
+            <v>3</v>
+          </cell>
+          <cell r="M20">
+            <v>1.7249999999999999</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21">
+            <v>39679</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>BRINDE BRINQUEDOS</v>
+          </cell>
+          <cell r="G21">
+            <v>0</v>
+          </cell>
+          <cell r="I21">
+            <v>0</v>
+          </cell>
+          <cell r="L21">
+            <v>0</v>
+          </cell>
+          <cell r="M21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22">
+            <v>39060</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v xml:space="preserve">BRINDE COPO </v>
+          </cell>
+          <cell r="G22">
+            <v>0</v>
+          </cell>
+          <cell r="I22">
+            <v>0</v>
+          </cell>
+          <cell r="L22">
+            <v>0</v>
+          </cell>
+          <cell r="M22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23">
+            <v>8791</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>ÁGUA GASEIFICADA H20 - 12UN</v>
+          </cell>
+          <cell r="G23">
+            <v>0</v>
+          </cell>
+          <cell r="I23">
+            <v>0</v>
+          </cell>
+          <cell r="L23">
+            <v>0</v>
+          </cell>
+          <cell r="M23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24">
+            <v>9085</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>GUARANA ANTARCTICA DIET LATA - 12UN</v>
+          </cell>
+          <cell r="G24">
+            <v>0</v>
+          </cell>
+          <cell r="I24">
+            <v>0</v>
+          </cell>
+          <cell r="L24">
+            <v>31</v>
+          </cell>
+          <cell r="M24">
+            <v>31</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25">
+            <v>9084</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>GUARANA ANTARCTICA LATA - 12UN</v>
+          </cell>
+          <cell r="G25">
+            <v>0</v>
+          </cell>
+          <cell r="I25">
+            <v>0</v>
+          </cell>
+          <cell r="L25">
+            <v>9</v>
+          </cell>
+          <cell r="M25">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26">
+            <v>9096</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>PEPSI COLA LATA - 12UN</v>
+          </cell>
+          <cell r="G26">
+            <v>0</v>
+          </cell>
+          <cell r="I26">
+            <v>0</v>
+          </cell>
+          <cell r="L26">
+            <v>53</v>
+          </cell>
+          <cell r="M26">
+            <v>53</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27">
+            <v>9274</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>PEPSI ZERO LATA - 12UN</v>
+          </cell>
+          <cell r="G27">
+            <v>0</v>
+          </cell>
+          <cell r="I27">
+            <v>0</v>
+          </cell>
+          <cell r="L27">
+            <v>18</v>
+          </cell>
+          <cell r="M27">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28">
+            <v>35047</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>SUCO DE MARACUJA - 12UN</v>
+          </cell>
+          <cell r="G28">
+            <v>0</v>
+          </cell>
+          <cell r="I28">
+            <v>0</v>
+          </cell>
+          <cell r="L28">
+            <v>33</v>
+          </cell>
+          <cell r="M28">
+            <v>33</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29">
+            <v>35959</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>SUCO LARANJA - 12UN</v>
+          </cell>
+          <cell r="G29">
+            <v>0</v>
+          </cell>
+          <cell r="I29">
+            <v>0</v>
+          </cell>
+          <cell r="L29">
+            <v>34</v>
+          </cell>
+          <cell r="M29">
+            <v>34</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30">
+            <v>35046</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>SUCO UVA - 12UN</v>
+          </cell>
+          <cell r="G30">
+            <v>0</v>
+          </cell>
+          <cell r="I30">
+            <v>0</v>
+          </cell>
+          <cell r="L30">
+            <v>3</v>
+          </cell>
+          <cell r="M30">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31">
+            <v>10143</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>CHA LIPTON LIMAO - 12UN</v>
+          </cell>
+          <cell r="G31">
+            <v>0</v>
+          </cell>
+          <cell r="I31">
+            <v>0</v>
+          </cell>
+          <cell r="L31">
+            <v>0</v>
+          </cell>
+          <cell r="M31">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32">
+            <v>10141</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>CHA LIPTON PESSEGO - 12UN</v>
+          </cell>
+          <cell r="G32">
+            <v>0</v>
+          </cell>
+          <cell r="I32">
+            <v>0</v>
+          </cell>
+          <cell r="L32">
+            <v>0</v>
+          </cell>
+          <cell r="M32">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="CONTAGEM_DIARIA_JUL25"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>Contagem DIARIA de Estoque  | BK Sorocaba Shopping | 26487</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>DATA:</v>
+          </cell>
+          <cell r="C4">
+            <v>45927</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>RESPONSÁVEL  DIU:</v>
+          </cell>
+          <cell r="F4" t="str">
+            <v>flavia</v>
+          </cell>
+          <cell r="J4" t="str">
+            <v>RESPONSÁVEL  NOT:</v>
+          </cell>
+          <cell r="L4" t="str">
+            <v>GUSTAVO</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>CÓD</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>DESCRIÇÃO</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>CONTAGEM  ABERTURA  (até 10h00)</v>
+          </cell>
+          <cell r="H5" t="str">
+            <v>RECEBIMENTO</v>
+          </cell>
+          <cell r="J5" t="str">
+            <v>CONTAGEM  FECHAMENTO  (após 22h00)</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="D6" t="str">
+            <v>CAIXA</v>
+          </cell>
+          <cell r="E6" t="str">
+            <v>PC ou FD</v>
+          </cell>
+          <cell r="F6" t="str">
+            <v>KG ou UND</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v>TOTAL</v>
+          </cell>
+          <cell r="H6" t="str">
+            <v>CAIXA</v>
+          </cell>
+          <cell r="I6" t="str">
+            <v>TOTAL</v>
+          </cell>
+          <cell r="J6" t="str">
+            <v>CAIXA</v>
+          </cell>
+          <cell r="K6" t="str">
+            <v>PC ou FD</v>
+          </cell>
+          <cell r="L6" t="str">
+            <v>KG ou UND</v>
+          </cell>
+          <cell r="M6" t="str">
+            <v>TOTAL</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>21403</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>CARNE CONG MOIDA WHOPPER - 152UN</v>
+          </cell>
+          <cell r="G7">
+            <v>0</v>
+          </cell>
+          <cell r="I7">
+            <v>0</v>
+          </cell>
+          <cell r="J7">
+            <v>4</v>
+          </cell>
+          <cell r="L7">
+            <v>73</v>
+          </cell>
+          <cell r="M7">
+            <v>681</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8">
+            <v>35622</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>CARNE HB MOIDA CONGELADA 2.0 - 333UN</v>
+          </cell>
+          <cell r="G8">
+            <v>0</v>
+          </cell>
+          <cell r="I8">
+            <v>0</v>
+          </cell>
+          <cell r="J8">
+            <v>2</v>
+          </cell>
+          <cell r="L8">
+            <v>315</v>
+          </cell>
+          <cell r="M8">
+            <v>981</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9">
+            <v>38178</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>HAMBURGUER BASE DE VEGETAIS 2.0 - 122UN</v>
+          </cell>
+          <cell r="G9">
+            <v>0</v>
+          </cell>
+          <cell r="I9">
+            <v>0</v>
+          </cell>
+          <cell r="L9">
+            <v>118</v>
+          </cell>
+          <cell r="M9">
+            <v>118</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>34580</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>BK CHICKEN - 588UN</v>
+          </cell>
+          <cell r="G10">
+            <v>0</v>
+          </cell>
+          <cell r="I10">
+            <v>0</v>
+          </cell>
+          <cell r="L10">
+            <v>48</v>
+          </cell>
+          <cell r="M10">
+            <v>48</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>36204</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>CHICKEN JR - 152UN</v>
+          </cell>
+          <cell r="G11">
+            <v>0</v>
+          </cell>
+          <cell r="I11">
+            <v>0</v>
+          </cell>
+          <cell r="J11">
+            <v>0</v>
+          </cell>
+          <cell r="K11">
+            <v>0</v>
+          </cell>
+          <cell r="L11">
+            <v>0</v>
+          </cell>
+          <cell r="M11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12">
+            <v>36206</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>TENDER CRISPY FILE - 72UN</v>
+          </cell>
+          <cell r="G12">
+            <v>0</v>
+          </cell>
+          <cell r="I12">
+            <v>0</v>
+          </cell>
+          <cell r="L12">
+            <v>16</v>
+          </cell>
+          <cell r="M12">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>35103</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>PAO HB CONG HAMBURGUER - 270UN</v>
+          </cell>
+          <cell r="G13">
+            <v>0</v>
+          </cell>
+          <cell r="I13">
+            <v>0</v>
+          </cell>
+          <cell r="J13">
+            <v>3</v>
+          </cell>
+          <cell r="K13">
+            <v>4</v>
+          </cell>
+          <cell r="L13">
+            <v>26</v>
+          </cell>
+          <cell r="M13">
+            <v>956</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14">
+            <v>38585</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>PAO BRIOCHE - 192UN</v>
+          </cell>
+          <cell r="G14">
+            <v>0</v>
+          </cell>
+          <cell r="I14">
+            <v>0</v>
+          </cell>
+          <cell r="K14">
+            <v>1</v>
+          </cell>
+          <cell r="L14">
+            <v>19</v>
+          </cell>
+          <cell r="M14">
+            <v>35</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15">
+            <v>36252</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>PAO SUPREMO - 180UN</v>
+          </cell>
+          <cell r="G15">
+            <v>0</v>
+          </cell>
+          <cell r="I15">
+            <v>0</v>
+          </cell>
+          <cell r="L15">
+            <v>1</v>
+          </cell>
+          <cell r="M15">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>34754</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>PAO WHOPPER - 120UN</v>
+          </cell>
+          <cell r="G16">
+            <v>0</v>
+          </cell>
+          <cell r="I16">
+            <v>0</v>
+          </cell>
+          <cell r="J16">
+            <v>3</v>
+          </cell>
+          <cell r="K16">
+            <v>4</v>
+          </cell>
+          <cell r="L16">
+            <v>16</v>
+          </cell>
+          <cell r="M16">
+            <v>456</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17">
+            <v>35619</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>QUEIJO CHEDDAR - 1536UN</v>
+          </cell>
+          <cell r="G17">
+            <v>0</v>
+          </cell>
+          <cell r="I17">
+            <v>0</v>
+          </cell>
+          <cell r="J17">
+            <v>2</v>
+          </cell>
+          <cell r="K17">
+            <v>1</v>
+          </cell>
+          <cell r="L17">
+            <v>190</v>
+          </cell>
+          <cell r="M17">
+            <v>3454</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18">
+            <v>21055</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>BATATA CONGELADA - 12,5K</v>
+          </cell>
+          <cell r="G18">
+            <v>0</v>
+          </cell>
+          <cell r="I18">
+            <v>0</v>
+          </cell>
+          <cell r="J18">
+            <v>9</v>
+          </cell>
+          <cell r="L18">
+            <v>0.1</v>
+          </cell>
+          <cell r="M18">
+            <v>112.6</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19">
+            <v>34298</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>BROWNIE BRIGADEIRO - 24UN</v>
+          </cell>
+          <cell r="G19">
+            <v>0</v>
+          </cell>
+          <cell r="I19">
+            <v>0</v>
+          </cell>
+          <cell r="L19">
+            <v>21</v>
+          </cell>
+          <cell r="M19">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20">
+            <v>39142</v>
+          </cell>
+          <cell r="C20" t="str">
+            <v>LEITE EM PÓ NINHO - 6,9KG</v>
+          </cell>
+          <cell r="G20">
+            <v>0</v>
+          </cell>
+          <cell r="I20">
+            <v>0</v>
+          </cell>
+          <cell r="K20">
+            <v>2</v>
+          </cell>
+          <cell r="M20">
+            <v>1.1499999999999999</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21">
+            <v>39679</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>BRINDE BRINQUEDOS</v>
+          </cell>
+          <cell r="G21">
+            <v>0</v>
+          </cell>
+          <cell r="I21">
+            <v>0</v>
+          </cell>
+          <cell r="M21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22">
+            <v>39060</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v xml:space="preserve">BRINDE COPO </v>
+          </cell>
+          <cell r="G22">
+            <v>0</v>
+          </cell>
+          <cell r="I22">
+            <v>0</v>
+          </cell>
+          <cell r="M22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23">
+            <v>8791</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>ÁGUA GASEIFICADA H20 - 12UN</v>
+          </cell>
+          <cell r="G23">
+            <v>0</v>
+          </cell>
+          <cell r="I23">
+            <v>0</v>
+          </cell>
+          <cell r="L23">
+            <v>8</v>
+          </cell>
+          <cell r="M23">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24">
+            <v>9085</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>GUARANA ANTARCTICA DIET LATA - 12UN</v>
+          </cell>
+          <cell r="G24">
+            <v>0</v>
+          </cell>
+          <cell r="I24">
+            <v>0</v>
+          </cell>
+          <cell r="J24">
+            <v>1</v>
+          </cell>
+          <cell r="M24">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25">
+            <v>9084</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>GUARANA ANTARCTICA LATA - 12UN</v>
+          </cell>
+          <cell r="G25">
+            <v>0</v>
+          </cell>
+          <cell r="I25">
+            <v>0</v>
+          </cell>
+          <cell r="J25">
+            <v>2</v>
+          </cell>
+          <cell r="L25">
+            <v>4</v>
+          </cell>
+          <cell r="M25">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26">
+            <v>9096</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>PEPSI COLA LATA - 12UN</v>
+          </cell>
+          <cell r="G26">
+            <v>0</v>
+          </cell>
+          <cell r="I26">
+            <v>0</v>
+          </cell>
+          <cell r="J26">
+            <v>4</v>
+          </cell>
+          <cell r="L26">
+            <v>2</v>
+          </cell>
+          <cell r="M26">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27">
+            <v>9274</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>PEPSI ZERO LATA - 12UN</v>
+          </cell>
+          <cell r="G27">
+            <v>0</v>
+          </cell>
+          <cell r="I27">
+            <v>0</v>
+          </cell>
+          <cell r="L27">
+            <v>6</v>
+          </cell>
+          <cell r="M27">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28">
+            <v>35047</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>SUCO DE MARACUJA - 12UN</v>
+          </cell>
+          <cell r="G28">
+            <v>0</v>
+          </cell>
+          <cell r="I28">
+            <v>0</v>
+          </cell>
+          <cell r="L28">
+            <v>18</v>
+          </cell>
+          <cell r="M28">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29">
+            <v>35959</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>SUCO LARANJA - 12UN</v>
+          </cell>
+          <cell r="G29">
+            <v>0</v>
+          </cell>
+          <cell r="I29">
+            <v>0</v>
+          </cell>
+          <cell r="L29">
+            <v>17</v>
+          </cell>
+          <cell r="M29">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30">
+            <v>35046</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>SUCO UVA - 12UN</v>
+          </cell>
+          <cell r="G30">
+            <v>0</v>
+          </cell>
+          <cell r="I30">
+            <v>0</v>
+          </cell>
+          <cell r="J30">
+            <v>2</v>
+          </cell>
+          <cell r="L30">
+            <v>6</v>
+          </cell>
+          <cell r="M30">
+            <v>30</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31">
+            <v>10143</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>CHA LIPTON LIMAO - 12UN</v>
+          </cell>
+          <cell r="G31">
+            <v>0</v>
+          </cell>
+          <cell r="I31">
+            <v>0</v>
+          </cell>
+          <cell r="L31">
+            <v>0</v>
+          </cell>
+          <cell r="M31">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32">
+            <v>10141</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>CHA LIPTON PESSEGO - 12UN</v>
+          </cell>
+          <cell r="G32">
+            <v>0</v>
+          </cell>
+          <cell r="I32">
+            <v>0</v>
+          </cell>
+          <cell r="L32">
+            <v>0</v>
+          </cell>
+          <cell r="M32">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1018,7 +2925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB15583B-E240-453F-9C06-A311E2614116}">
-  <dimension ref="A1:I169"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38.5703125" customWidth="1"/>
@@ -1026,7 +2933,7 @@
     <col min="6" max="6" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>168</v>
       </c>
@@ -1047,10 +2954,22 @@
         <v>170</v>
       </c>
       <c r="I1" s="10">
-        <v>45868</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>45886</v>
+      </c>
+      <c r="J1" t="s">
+        <v>171</v>
+      </c>
+      <c r="K1" s="10">
+        <v>45894</v>
+      </c>
+      <c r="L1" t="s">
+        <v>172</v>
+      </c>
+      <c r="M1" s="10">
+        <v>45927</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>8791</v>
       </c>
@@ -1058,7 +2977,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
@@ -1069,11 +2988,28 @@
       <c r="H2" s="11">
         <v>-6</v>
       </c>
-      <c r="I2" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <f>IFERROR(VLOOKUP(A2,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>IF(I2="NA",C2,I2)</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>IFERROR(VLOOKUP(A2,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>IF(K2="NAO",C2,K2)</f>
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <f>VLOOKUP(A2,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>10138</v>
       </c>
@@ -1092,11 +3028,28 @@
       <c r="H3" s="11">
         <v>0</v>
       </c>
-      <c r="I3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I3" t="str">
+        <f>IFERROR(VLOOKUP(A3,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J3">
+        <f>IF(I3="NA",C3,I3)</f>
+        <v>0</v>
+      </c>
+      <c r="K3" t="str">
+        <f>IFERROR(VLOOKUP(A3,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L66" si="0">IF(K3="NAO",C3,K3)</f>
+        <v>0</v>
+      </c>
+      <c r="M3" t="e">
+        <f>VLOOKUP(A3,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3029</v>
       </c>
@@ -1115,11 +3068,28 @@
       <c r="H4" s="11">
         <v>2</v>
       </c>
-      <c r="I4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I4" t="str">
+        <f>IFERROR(VLOOKUP(A4,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J4">
+        <f>IF(I4="NA",C4,I4)</f>
+        <v>17</v>
+      </c>
+      <c r="K4" t="str">
+        <f>IFERROR(VLOOKUP(A4,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="M4" t="e">
+        <f>VLOOKUP(A4,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>19634</v>
       </c>
@@ -1138,11 +3108,28 @@
       <c r="H5" s="11">
         <v>-6.492</v>
       </c>
-      <c r="I5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5" t="str">
+        <f>IFERROR(VLOOKUP(A5,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J5">
+        <f>IF(I5="NA",C5,I5)</f>
+        <v>6.492</v>
+      </c>
+      <c r="K5" t="str">
+        <f>IFERROR(VLOOKUP(A5,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="0"/>
+        <v>6.492</v>
+      </c>
+      <c r="M5" t="e">
+        <f>VLOOKUP(A5,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>21358</v>
       </c>
@@ -1161,11 +3148,28 @@
       <c r="H6" s="11">
         <v>0</v>
       </c>
-      <c r="I6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6" t="str">
+        <f>IFERROR(VLOOKUP(A6,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J6">
+        <f>IF(I6="NA",C6,I6)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" t="str">
+        <f>IFERROR(VLOOKUP(A6,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M6" t="e">
+        <f>VLOOKUP(A6,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>21317</v>
       </c>
@@ -1184,11 +3188,28 @@
       <c r="H7" s="11">
         <v>-1.2680000000000002</v>
       </c>
-      <c r="I7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I7" t="str">
+        <f>IFERROR(VLOOKUP(A7,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J7">
+        <f t="shared" ref="J7:J66" si="1">IF(I7="NA",C7,I7)</f>
+        <v>2.4980000000000002</v>
+      </c>
+      <c r="K7" t="str">
+        <f>IFERROR(VLOOKUP(A7,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>2.4980000000000002</v>
+      </c>
+      <c r="M7" t="e">
+        <f>VLOOKUP(A7,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>28582</v>
       </c>
@@ -1207,11 +3228,28 @@
       <c r="H8" s="11">
         <v>-664.38</v>
       </c>
-      <c r="I8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I8" t="str">
+        <f>IFERROR(VLOOKUP(A8,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>664.38</v>
+      </c>
+      <c r="K8" t="str">
+        <f>IFERROR(VLOOKUP(A8,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>664.38</v>
+      </c>
+      <c r="M8" t="e">
+        <f>VLOOKUP(A8,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>37839</v>
       </c>
@@ -1230,11 +3268,28 @@
       <c r="H9" s="11">
         <v>0</v>
       </c>
-      <c r="I9" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I9" t="str">
+        <f>IFERROR(VLOOKUP(A9,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K9" t="str">
+        <f>IFERROR(VLOOKUP(A9,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M9" t="e">
+        <f>VLOOKUP(A9,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>37840</v>
       </c>
@@ -1253,11 +3308,28 @@
       <c r="H10" s="11">
         <v>0</v>
       </c>
-      <c r="I10" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I10" t="str">
+        <f>IFERROR(VLOOKUP(A10,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K10" t="str">
+        <f>IFERROR(VLOOKUP(A10,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M10" t="e">
+        <f>VLOOKUP(A10,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>26290</v>
       </c>
@@ -1276,11 +3348,28 @@
       <c r="H11" s="11">
         <v>413</v>
       </c>
-      <c r="I11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I11" t="str">
+        <f>IFERROR(VLOOKUP(A11,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>489</v>
+      </c>
+      <c r="K11" t="str">
+        <f>IFERROR(VLOOKUP(A11,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>489</v>
+      </c>
+      <c r="M11" t="e">
+        <f>VLOOKUP(A11,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>36305</v>
       </c>
@@ -1299,11 +3388,28 @@
       <c r="H12" s="11">
         <v>0</v>
       </c>
-      <c r="I12" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I12" t="str">
+        <f>IFERROR(VLOOKUP(A12,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K12" t="str">
+        <f>IFERROR(VLOOKUP(A12,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M12" t="e">
+        <f>VLOOKUP(A12,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>37744</v>
       </c>
@@ -1322,11 +3428,28 @@
       <c r="H13" s="11">
         <v>0</v>
       </c>
-      <c r="I13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I13" t="str">
+        <f>IFERROR(VLOOKUP(A13,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K13" t="str">
+        <f>IFERROR(VLOOKUP(A13,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M13" t="e">
+        <f>VLOOKUP(A13,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>21055</v>
       </c>
@@ -1334,7 +3457,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="4">
-        <v>37.5</v>
+        <v>112.6</v>
       </c>
       <c r="F14" s="4">
         <v>19.61</v>
@@ -1345,11 +3468,28 @@
       <c r="H14" s="11">
         <v>-32.302</v>
       </c>
-      <c r="I14" s="12">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I14">
+        <f>IFERROR(VLOOKUP(A14,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>86.98</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="1"/>
+        <v>86.98</v>
+      </c>
+      <c r="K14">
+        <f>IFERROR(VLOOKUP(A14,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>25.308</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="0"/>
+        <v>25.308</v>
+      </c>
+      <c r="M14">
+        <f>VLOOKUP(A14,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>112.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>28459</v>
       </c>
@@ -1368,11 +3508,28 @@
       <c r="H15" s="11">
         <v>-22</v>
       </c>
-      <c r="I15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" t="str">
+        <f>IFERROR(VLOOKUP(A15,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="K15" t="str">
+        <f>IFERROR(VLOOKUP(A15,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="M15" t="e">
+        <f>VLOOKUP(A15,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>33057</v>
       </c>
@@ -1391,11 +3548,28 @@
       <c r="H16" s="11">
         <v>-11</v>
       </c>
-      <c r="I16" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I16" t="str">
+        <f>IFERROR(VLOOKUP(A16,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="K16" t="str">
+        <f>IFERROR(VLOOKUP(A16,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="M16" t="e">
+        <f>VLOOKUP(A16,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>34580</v>
       </c>
@@ -1403,7 +3577,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="4">
-        <v>483</v>
+        <v>48</v>
       </c>
       <c r="F17" s="4">
         <v>92</v>
@@ -1414,11 +3588,28 @@
       <c r="H17" s="11">
         <v>92</v>
       </c>
-      <c r="I17" s="12">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I17">
+        <f>IFERROR(VLOOKUP(A17,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>360</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="K17">
+        <f>IFERROR(VLOOKUP(A17,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>71</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="M17">
+        <f>VLOOKUP(A17,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>24754</v>
       </c>
@@ -1426,7 +3617,7 @@
         <v>162</v>
       </c>
       <c r="C18" s="4">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="F18" s="4">
         <v>0</v>
@@ -1437,11 +3628,28 @@
       <c r="H18" s="11">
         <v>0</v>
       </c>
-      <c r="I18" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I18" t="str">
+        <f>IFERROR(VLOOKUP(A18,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="K18" t="str">
+        <f>IFERROR(VLOOKUP(A18,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+      <c r="M18" t="e">
+        <f>VLOOKUP(A18,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>38838</v>
       </c>
@@ -1460,11 +3668,28 @@
       <c r="H19" s="11">
         <v>0</v>
       </c>
-      <c r="I19" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I19" t="str">
+        <f>IFERROR(VLOOKUP(A19,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K19" t="str">
+        <f>IFERROR(VLOOKUP(A19,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M19" t="e">
+        <f>VLOOKUP(A19,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>38008</v>
       </c>
@@ -1483,11 +3708,28 @@
       <c r="H20" s="11">
         <v>4.5280000000000005</v>
       </c>
-      <c r="I20" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I20" t="str">
+        <f>IFERROR(VLOOKUP(A20,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K20" t="str">
+        <f>IFERROR(VLOOKUP(A20,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M20" t="e">
+        <f>VLOOKUP(A20,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>39679</v>
       </c>
@@ -1506,11 +3748,28 @@
       <c r="H21" s="11">
         <v>0</v>
       </c>
-      <c r="I21" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I21">
+        <f>IFERROR(VLOOKUP(A21,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <f>IFERROR(VLOOKUP(A21,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <f>VLOOKUP(A21,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>39060</v>
       </c>
@@ -1529,11 +3788,28 @@
       <c r="H22" s="11">
         <v>0</v>
       </c>
-      <c r="I22" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I22">
+        <f>IFERROR(VLOOKUP(A22,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <f>IFERROR(VLOOKUP(A22,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f>VLOOKUP(A22,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>34298</v>
       </c>
@@ -1541,7 +3817,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F23" s="4">
         <v>8</v>
@@ -1552,11 +3828,28 @@
       <c r="H23" s="11">
         <v>8</v>
       </c>
-      <c r="I23" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I23">
+        <f>IFERROR(VLOOKUP(A23,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>25</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="K23">
+        <f>IFERROR(VLOOKUP(A23,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>17</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="M23">
+        <f>VLOOKUP(A23,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>33919</v>
       </c>
@@ -1575,11 +3868,28 @@
       <c r="H24" s="11">
         <v>5.0000000000000044E-3</v>
       </c>
-      <c r="I24" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I24" t="str">
+        <f>IFERROR(VLOOKUP(A24,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="1"/>
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="K24" t="str">
+        <f>IFERROR(VLOOKUP(A24,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="0"/>
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="M24" t="e">
+        <f>VLOOKUP(A24,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>38577</v>
       </c>
@@ -1598,11 +3908,28 @@
       <c r="H25" s="11">
         <v>4</v>
       </c>
-      <c r="I25" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I25" t="str">
+        <f>IFERROR(VLOOKUP(A25,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="K25" t="str">
+        <f>IFERROR(VLOOKUP(A25,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="M25" t="e">
+        <f>VLOOKUP(A25,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>38007</v>
       </c>
@@ -1621,11 +3948,28 @@
       <c r="H26" s="11">
         <v>0</v>
       </c>
-      <c r="I26" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I26" t="str">
+        <f>IFERROR(VLOOKUP(A26,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K26" t="str">
+        <f>IFERROR(VLOOKUP(A26,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M26" t="e">
+        <f>VLOOKUP(A26,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>37986</v>
       </c>
@@ -1644,11 +3988,28 @@
       <c r="H27" s="11">
         <v>0</v>
       </c>
-      <c r="I27" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I27" t="str">
+        <f>IFERROR(VLOOKUP(A27,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K27" t="str">
+        <f>IFERROR(VLOOKUP(A27,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M27" t="e">
+        <f>VLOOKUP(A27,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>38454</v>
       </c>
@@ -1667,11 +4028,28 @@
       <c r="H28" s="11">
         <v>0</v>
       </c>
-      <c r="I28" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I28" t="str">
+        <f>IFERROR(VLOOKUP(A28,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K28" t="str">
+        <f>IFERROR(VLOOKUP(A28,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M28" t="e">
+        <f>VLOOKUP(A28,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>30153</v>
       </c>
@@ -1690,11 +4068,28 @@
       <c r="H29" s="11">
         <v>-8.1999999999999851E-2</v>
       </c>
-      <c r="I29" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I29" t="str">
+        <f>IFERROR(VLOOKUP(A29,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="1"/>
+        <v>7.79</v>
+      </c>
+      <c r="K29" t="str">
+        <f>IFERROR(VLOOKUP(A29,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="0"/>
+        <v>7.79</v>
+      </c>
+      <c r="M29" t="e">
+        <f>VLOOKUP(A29,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>34599</v>
       </c>
@@ -1713,11 +4108,28 @@
       <c r="H30" s="11">
         <v>-0.14199999999999946</v>
       </c>
-      <c r="I30" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I30" t="str">
+        <f>IFERROR(VLOOKUP(A30,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="1"/>
+        <v>17.248000000000001</v>
+      </c>
+      <c r="K30" t="str">
+        <f>IFERROR(VLOOKUP(A30,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="0"/>
+        <v>17.248000000000001</v>
+      </c>
+      <c r="M30" t="e">
+        <f>VLOOKUP(A30,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30413</v>
       </c>
@@ -1736,11 +4148,28 @@
       <c r="H31" s="11">
         <v>50</v>
       </c>
-      <c r="I31" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I31" t="str">
+        <f>IFERROR(VLOOKUP(A31,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+      <c r="K31" t="str">
+        <f>IFERROR(VLOOKUP(A31,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="M31" t="e">
+        <f>VLOOKUP(A31,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>29842</v>
       </c>
@@ -1759,11 +4188,28 @@
       <c r="H32" s="11">
         <v>-23</v>
       </c>
-      <c r="I32" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I32" t="str">
+        <f>IFERROR(VLOOKUP(A32,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="1"/>
+        <v>1023</v>
+      </c>
+      <c r="K32" t="str">
+        <f>IFERROR(VLOOKUP(A32,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="0"/>
+        <v>1023</v>
+      </c>
+      <c r="M32" t="e">
+        <f>VLOOKUP(A32,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>21403</v>
       </c>
@@ -1771,7 +4217,7 @@
         <v>30</v>
       </c>
       <c r="C33" s="4">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="F33" s="4">
         <v>235</v>
@@ -1782,11 +4228,28 @@
       <c r="H33" s="11">
         <v>-15</v>
       </c>
-      <c r="I33" s="12">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I33">
+        <f>IFERROR(VLOOKUP(A33,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>456</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="1"/>
+        <v>456</v>
+      </c>
+      <c r="K33">
+        <f>IFERROR(VLOOKUP(A33,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>26</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="M33">
+        <f>VLOOKUP(A33,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>681</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>35221</v>
       </c>
@@ -1805,11 +4268,28 @@
       <c r="H34" s="11">
         <v>0</v>
       </c>
-      <c r="I34" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I34" t="str">
+        <f>IFERROR(VLOOKUP(A34,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K34" t="str">
+        <f>IFERROR(VLOOKUP(A34,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M34" t="e">
+        <f>VLOOKUP(A34,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>35622</v>
       </c>
@@ -1817,7 +4297,7 @@
         <v>32</v>
       </c>
       <c r="C35" s="4">
-        <v>1027</v>
+        <v>981</v>
       </c>
       <c r="F35" s="4">
         <v>0</v>
@@ -1828,11 +4308,27 @@
       <c r="H35" s="11">
         <v>-1</v>
       </c>
-      <c r="I35" s="12">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I35">
+        <f>IFERROR(VLOOKUP(A35,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>1061</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="1"/>
+        <v>1061</v>
+      </c>
+      <c r="K35" t="str">
+        <f>IFERROR(VLOOKUP(A35,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <f>VLOOKUP(A35,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>981</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>36409</v>
       </c>
@@ -1840,7 +4336,7 @@
         <v>167</v>
       </c>
       <c r="C36" s="4">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="F36" s="4">
         <v>0</v>
@@ -1851,11 +4347,28 @@
       <c r="H36" s="11">
         <v>0</v>
       </c>
-      <c r="I36" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I36" t="str">
+        <f>IFERROR(VLOOKUP(A36,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="1"/>
+        <v>981</v>
+      </c>
+      <c r="K36">
+        <f>IFERROR(VLOOKUP(A36,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>825</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="0"/>
+        <v>825</v>
+      </c>
+      <c r="M36" t="e">
+        <f>VLOOKUP(A36,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>31192</v>
       </c>
@@ -1874,11 +4387,28 @@
       <c r="H37" s="11">
         <v>78</v>
       </c>
-      <c r="I37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I37" t="str">
+        <f>IFERROR(VLOOKUP(A37,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="K37" t="str">
+        <f>IFERROR(VLOOKUP(A37,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="M37" t="e">
+        <f>VLOOKUP(A37,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>35051</v>
       </c>
@@ -1897,11 +4427,28 @@
       <c r="H38" s="11">
         <v>2035</v>
       </c>
-      <c r="I38" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I38" t="str">
+        <f>IFERROR(VLOOKUP(A38,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="1"/>
+        <v>2450</v>
+      </c>
+      <c r="K38" t="str">
+        <f>IFERROR(VLOOKUP(A38,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="0"/>
+        <v>2450</v>
+      </c>
+      <c r="M38" t="e">
+        <f>VLOOKUP(A38,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>35293</v>
       </c>
@@ -1909,7 +4456,7 @@
         <v>161</v>
       </c>
       <c r="C39" s="4">
-        <v>0</v>
+        <v>2450</v>
       </c>
       <c r="F39" s="4">
         <v>0</v>
@@ -1920,11 +4467,28 @@
       <c r="H39" s="11">
         <v>0</v>
       </c>
-      <c r="I39" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I39" t="str">
+        <f>IFERROR(VLOOKUP(A39,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="1"/>
+        <v>2450</v>
+      </c>
+      <c r="K39" t="str">
+        <f>IFERROR(VLOOKUP(A39,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="0"/>
+        <v>2450</v>
+      </c>
+      <c r="M39" t="e">
+        <f>VLOOKUP(A39,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>32575</v>
       </c>
@@ -1943,11 +4507,28 @@
       <c r="H40" s="11">
         <v>-570</v>
       </c>
-      <c r="I40" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I40" t="str">
+        <f>IFERROR(VLOOKUP(A40,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="1"/>
+        <v>670</v>
+      </c>
+      <c r="K40" t="str">
+        <f>IFERROR(VLOOKUP(A40,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="M40" t="e">
+        <f>VLOOKUP(A40,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>38707</v>
       </c>
@@ -1966,11 +4547,28 @@
       <c r="H41" s="11">
         <v>3</v>
       </c>
-      <c r="I41" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I41" t="str">
+        <f>IFERROR(VLOOKUP(A41,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K41" t="str">
+        <f>IFERROR(VLOOKUP(A41,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M41" t="e">
+        <f>VLOOKUP(A41,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>38686</v>
       </c>
@@ -1989,11 +4587,28 @@
       <c r="H42" s="11">
         <v>0</v>
       </c>
-      <c r="I42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I42" t="str">
+        <f>IFERROR(VLOOKUP(A42,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K42" t="str">
+        <f>IFERROR(VLOOKUP(A42,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M42" t="e">
+        <f>VLOOKUP(A42,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>3841</v>
       </c>
@@ -2012,11 +4627,28 @@
       <c r="H43" s="11">
         <v>85</v>
       </c>
-      <c r="I43" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I43" t="str">
+        <f>IFERROR(VLOOKUP(A43,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="1"/>
+        <v>435</v>
+      </c>
+      <c r="K43" t="str">
+        <f>IFERROR(VLOOKUP(A43,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="0"/>
+        <v>435</v>
+      </c>
+      <c r="M43" t="e">
+        <f>VLOOKUP(A43,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>25622</v>
       </c>
@@ -2035,11 +4667,28 @@
       <c r="H44" s="11">
         <v>-0.2</v>
       </c>
-      <c r="I44" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I44" t="str">
+        <f>IFERROR(VLOOKUP(A44,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="K44" t="str">
+        <f>IFERROR(VLOOKUP(A44,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="M44" t="e">
+        <f>VLOOKUP(A44,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>35531</v>
       </c>
@@ -2058,11 +4707,28 @@
       <c r="H45" s="11">
         <v>2.0580000000000003</v>
       </c>
-      <c r="I45" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I45" t="str">
+        <f>IFERROR(VLOOKUP(A45,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="1"/>
+        <v>3.18</v>
+      </c>
+      <c r="K45" t="str">
+        <f>IFERROR(VLOOKUP(A45,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="0"/>
+        <v>3.18</v>
+      </c>
+      <c r="M45" t="e">
+        <f>VLOOKUP(A45,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>10143</v>
       </c>
@@ -2081,11 +4747,28 @@
       <c r="H46" s="11">
         <v>0</v>
       </c>
-      <c r="I46" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I46">
+        <f>IFERROR(VLOOKUP(A46,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <f>IFERROR(VLOOKUP(A46,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <f>VLOOKUP(A46,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>10141</v>
       </c>
@@ -2104,11 +4787,28 @@
       <c r="H47" s="11">
         <v>0</v>
       </c>
-      <c r="I47" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I47">
+        <f>IFERROR(VLOOKUP(A47,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <f>IFERROR(VLOOKUP(A47,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <f>VLOOKUP(A47,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>36204</v>
       </c>
@@ -2116,7 +4816,7 @@
         <v>43</v>
       </c>
       <c r="C48" s="4">
-        <v>145</v>
+        <v>12</v>
       </c>
       <c r="F48" s="4">
         <v>0</v>
@@ -2127,11 +4827,27 @@
       <c r="H48" s="11">
         <v>-3</v>
       </c>
-      <c r="I48" s="12">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I48">
+        <f>IFERROR(VLOOKUP(A48,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>204</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="1"/>
+        <v>204</v>
+      </c>
+      <c r="K48" t="str">
+        <f>IFERROR(VLOOKUP(A48,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <f>VLOOKUP(A48,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
         <v>31777</v>
       </c>
@@ -2139,7 +4855,7 @@
         <v>43</v>
       </c>
       <c r="C49" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F49" s="4">
         <v>0</v>
@@ -2150,11 +4866,28 @@
       <c r="H49" s="11">
         <v>0</v>
       </c>
-      <c r="I49" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I49" t="str">
+        <f>IFERROR(VLOOKUP(A49,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="K49">
+        <f>IFERROR(VLOOKUP(A49,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>12</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="M49" t="e">
+        <f>VLOOKUP(A49,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>38711</v>
       </c>
@@ -2173,11 +4906,28 @@
       <c r="H50" s="11">
         <v>0</v>
       </c>
-      <c r="I50" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I50" t="str">
+        <f>IFERROR(VLOOKUP(A50,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K50" t="str">
+        <f>IFERROR(VLOOKUP(A50,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M50" t="e">
+        <f>VLOOKUP(A50,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>36394</v>
       </c>
@@ -2196,11 +4946,28 @@
       <c r="H51" s="11">
         <v>0</v>
       </c>
-      <c r="I51" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I51" t="str">
+        <f>IFERROR(VLOOKUP(A51,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K51" t="str">
+        <f>IFERROR(VLOOKUP(A51,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M51" t="e">
+        <f>VLOOKUP(A51,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>37801</v>
       </c>
@@ -2219,11 +4986,28 @@
       <c r="H52" s="11">
         <v>0</v>
       </c>
-      <c r="I52" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I52" t="str">
+        <f>IFERROR(VLOOKUP(A52,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K52" t="str">
+        <f>IFERROR(VLOOKUP(A52,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M52" t="e">
+        <f>VLOOKUP(A52,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>35642</v>
       </c>
@@ -2242,11 +5026,28 @@
       <c r="H53" s="11">
         <v>-0.37999999999999989</v>
       </c>
-      <c r="I53" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I53" t="str">
+        <f>IFERROR(VLOOKUP(A53,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="1"/>
+        <v>2.48</v>
+      </c>
+      <c r="K53" t="str">
+        <f>IFERROR(VLOOKUP(A53,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="0"/>
+        <v>2.48</v>
+      </c>
+      <c r="M53" t="e">
+        <f>VLOOKUP(A53,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>25997</v>
       </c>
@@ -2265,11 +5066,28 @@
       <c r="H54" s="11">
         <v>90</v>
       </c>
-      <c r="I54" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I54" t="str">
+        <f>IFERROR(VLOOKUP(A54,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="K54" t="str">
+        <f>IFERROR(VLOOKUP(A54,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M54" t="e">
+        <f>VLOOKUP(A54,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>30482</v>
       </c>
@@ -2288,11 +5106,28 @@
       <c r="H55" s="11">
         <v>0</v>
       </c>
-      <c r="I55" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I55" t="str">
+        <f>IFERROR(VLOOKUP(A55,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K55" t="str">
+        <f>IFERROR(VLOOKUP(A55,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M55" t="e">
+        <f>VLOOKUP(A55,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>32699</v>
       </c>
@@ -2311,11 +5146,28 @@
       <c r="H56" s="11">
         <v>-138</v>
       </c>
-      <c r="I56" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I56" t="str">
+        <f>IFERROR(VLOOKUP(A56,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="1"/>
+        <v>938</v>
+      </c>
+      <c r="K56" t="str">
+        <f>IFERROR(VLOOKUP(A56,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L56">
+        <f t="shared" si="0"/>
+        <v>938</v>
+      </c>
+      <c r="M56" t="e">
+        <f>VLOOKUP(A56,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>24016</v>
       </c>
@@ -2334,11 +5186,28 @@
       <c r="H57" s="11">
         <v>-238</v>
       </c>
-      <c r="I57" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I57" t="str">
+        <f>IFERROR(VLOOKUP(A57,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="1"/>
+        <v>538</v>
+      </c>
+      <c r="K57" t="str">
+        <f>IFERROR(VLOOKUP(A57,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L57">
+        <f t="shared" si="0"/>
+        <v>538</v>
+      </c>
+      <c r="M57" t="e">
+        <f>VLOOKUP(A57,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>24013</v>
       </c>
@@ -2357,11 +5226,28 @@
       <c r="H58" s="11">
         <v>0</v>
       </c>
-      <c r="I58" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I58" t="str">
+        <f>IFERROR(VLOOKUP(A58,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K58" t="str">
+        <f>IFERROR(VLOOKUP(A58,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M58" t="e">
+        <f>VLOOKUP(A58,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>35707</v>
       </c>
@@ -2380,11 +5266,28 @@
       <c r="H59" s="11">
         <v>0</v>
       </c>
-      <c r="I59" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I59" t="str">
+        <f>IFERROR(VLOOKUP(A59,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K59" t="str">
+        <f>IFERROR(VLOOKUP(A59,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M59" t="e">
+        <f>VLOOKUP(A59,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>14321</v>
       </c>
@@ -2403,11 +5306,28 @@
       <c r="H60" s="11">
         <v>-648</v>
       </c>
-      <c r="I60" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I60" t="str">
+        <f>IFERROR(VLOOKUP(A60,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="1"/>
+        <v>1548</v>
+      </c>
+      <c r="K60" t="str">
+        <f>IFERROR(VLOOKUP(A60,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="0"/>
+        <v>1548</v>
+      </c>
+      <c r="M60" t="e">
+        <f>VLOOKUP(A60,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>32677</v>
       </c>
@@ -2426,11 +5346,28 @@
       <c r="H61" s="11">
         <v>38</v>
       </c>
-      <c r="I61" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I61" t="str">
+        <f>IFERROR(VLOOKUP(A61,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="1"/>
+        <v>312</v>
+      </c>
+      <c r="K61" t="str">
+        <f>IFERROR(VLOOKUP(A61,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="0"/>
+        <v>312</v>
+      </c>
+      <c r="M61" t="e">
+        <f>VLOOKUP(A61,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>32678</v>
       </c>
@@ -2449,11 +5386,28 @@
       <c r="H62" s="11">
         <v>-7</v>
       </c>
-      <c r="I62" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I62" t="str">
+        <f>IFERROR(VLOOKUP(A62,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="1"/>
+        <v>167</v>
+      </c>
+      <c r="K62" t="str">
+        <f>IFERROR(VLOOKUP(A62,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="0"/>
+        <v>167</v>
+      </c>
+      <c r="M62" t="e">
+        <f>VLOOKUP(A62,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>36073</v>
       </c>
@@ -2472,11 +5426,28 @@
       <c r="H63" s="11">
         <v>0</v>
       </c>
-      <c r="I63" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I63" t="str">
+        <f>IFERROR(VLOOKUP(A63,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K63" t="str">
+        <f>IFERROR(VLOOKUP(A63,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M63" t="e">
+        <f>VLOOKUP(A63,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>38537</v>
       </c>
@@ -2495,11 +5466,28 @@
       <c r="H64" s="11">
         <v>0</v>
       </c>
-      <c r="I64" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I64" t="str">
+        <f>IFERROR(VLOOKUP(A64,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K64" t="str">
+        <f>IFERROR(VLOOKUP(A64,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M64" t="e">
+        <f>VLOOKUP(A64,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>31161</v>
       </c>
@@ -2518,11 +5506,28 @@
       <c r="H65" s="11">
         <v>-4.5880000000000001</v>
       </c>
-      <c r="I65" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I65" t="str">
+        <f>IFERROR(VLOOKUP(A65,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="1"/>
+        <v>6.3079999999999998</v>
+      </c>
+      <c r="K65" t="str">
+        <f>IFERROR(VLOOKUP(A65,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="0"/>
+        <v>6.3079999999999998</v>
+      </c>
+      <c r="M65" t="e">
+        <f>VLOOKUP(A65,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>38956</v>
       </c>
@@ -2541,11 +5546,28 @@
       <c r="H66" s="11">
         <v>0.11799999999999988</v>
       </c>
-      <c r="I66" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I66" t="str">
+        <f>IFERROR(VLOOKUP(A66,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="1"/>
+        <v>3.6120000000000001</v>
+      </c>
+      <c r="K66" t="str">
+        <f>IFERROR(VLOOKUP(A66,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="0"/>
+        <v>3.6120000000000001</v>
+      </c>
+      <c r="M66" t="e">
+        <f>VLOOKUP(A66,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>35919</v>
       </c>
@@ -2564,11 +5586,28 @@
       <c r="H67" s="11">
         <v>-12.632</v>
       </c>
-      <c r="I67" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I67" t="str">
+        <f>IFERROR(VLOOKUP(A67,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J67">
+        <f t="shared" ref="J67:J130" si="2">IF(I67="NA",C67,I67)</f>
+        <v>12.632</v>
+      </c>
+      <c r="K67" t="str">
+        <f>IFERROR(VLOOKUP(A67,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L67">
+        <f t="shared" ref="L67:L130" si="3">IF(K67="NAO",C67,K67)</f>
+        <v>12.632</v>
+      </c>
+      <c r="M67" t="e">
+        <f>VLOOKUP(A67,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>29750</v>
       </c>
@@ -2587,11 +5626,28 @@
       <c r="H68" s="11">
         <v>1482</v>
       </c>
-      <c r="I68" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I68" t="str">
+        <f>IFERROR(VLOOKUP(A68,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="2"/>
+        <v>750</v>
+      </c>
+      <c r="K68" t="str">
+        <f>IFERROR(VLOOKUP(A68,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="3"/>
+        <v>750</v>
+      </c>
+      <c r="M68" t="e">
+        <f>VLOOKUP(A68,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>22154</v>
       </c>
@@ -2610,11 +5666,28 @@
       <c r="H69" s="11">
         <v>85</v>
       </c>
-      <c r="I69" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I69" t="str">
+        <f>IFERROR(VLOOKUP(A69,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="2"/>
+        <v>465</v>
+      </c>
+      <c r="K69" t="str">
+        <f>IFERROR(VLOOKUP(A69,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="3"/>
+        <v>465</v>
+      </c>
+      <c r="M69" t="e">
+        <f>VLOOKUP(A69,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>31196</v>
       </c>
@@ -2633,11 +5706,28 @@
       <c r="H70" s="11">
         <v>130</v>
       </c>
-      <c r="I70" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I70" t="str">
+        <f>IFERROR(VLOOKUP(A70,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+      <c r="K70" t="str">
+        <f>IFERROR(VLOOKUP(A70,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="3"/>
+        <v>135</v>
+      </c>
+      <c r="M70" t="e">
+        <f>VLOOKUP(A70,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>32387</v>
       </c>
@@ -2656,11 +5746,28 @@
       <c r="H71" s="11">
         <v>-144</v>
       </c>
-      <c r="I71" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I71" t="str">
+        <f>IFERROR(VLOOKUP(A71,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="2"/>
+        <v>1335</v>
+      </c>
+      <c r="K71" t="str">
+        <f>IFERROR(VLOOKUP(A71,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="3"/>
+        <v>1335</v>
+      </c>
+      <c r="M71" t="e">
+        <f>VLOOKUP(A71,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>35057</v>
       </c>
@@ -2679,11 +5786,28 @@
       <c r="H72" s="11">
         <v>0</v>
       </c>
-      <c r="I72" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I72" t="str">
+        <f>IFERROR(VLOOKUP(A72,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K72" t="str">
+        <f>IFERROR(VLOOKUP(A72,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L72">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M72" t="e">
+        <f>VLOOKUP(A72,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>2250</v>
       </c>
@@ -2702,11 +5826,28 @@
       <c r="H73" s="11">
         <v>-13</v>
       </c>
-      <c r="I73" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I73" t="str">
+        <f>IFERROR(VLOOKUP(A73,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="K73" t="str">
+        <f>IFERROR(VLOOKUP(A73,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L73">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="M73" t="e">
+        <f>VLOOKUP(A73,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>2243</v>
       </c>
@@ -2725,11 +5866,28 @@
       <c r="H74" s="11">
         <v>23</v>
       </c>
-      <c r="I74" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I74" t="str">
+        <f>IFERROR(VLOOKUP(A74,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="K74" t="str">
+        <f>IFERROR(VLOOKUP(A74,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L74">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="M74" t="e">
+        <f>VLOOKUP(A74,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>9085</v>
       </c>
@@ -2737,7 +5895,7 @@
         <v>69</v>
       </c>
       <c r="C75" s="4">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="F75" s="4">
         <v>36</v>
@@ -2748,11 +5906,28 @@
       <c r="H75" s="11">
         <v>20</v>
       </c>
-      <c r="I75" s="12">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I75">
+        <f>IFERROR(VLOOKUP(A75,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <f>IFERROR(VLOOKUP(A75,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>31</v>
+      </c>
+      <c r="L75">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="M75">
+        <f>VLOOKUP(A75,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>9084</v>
       </c>
@@ -2760,7 +5935,7 @@
         <v>70</v>
       </c>
       <c r="C76" s="4">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="F76" s="4">
         <v>0</v>
@@ -2771,11 +5946,28 @@
       <c r="H76" s="11">
         <v>-24</v>
       </c>
-      <c r="I76" s="12">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I76">
+        <f>IFERROR(VLOOKUP(A76,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <f>IFERROR(VLOOKUP(A76,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>9</v>
+      </c>
+      <c r="L76">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="M76">
+        <f>VLOOKUP(A76,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>3043</v>
       </c>
@@ -2794,11 +5986,28 @@
       <c r="H77" s="11">
         <v>1432</v>
       </c>
-      <c r="I77" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I77" t="str">
+        <f>IFERROR(VLOOKUP(A77,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="2"/>
+        <v>2448</v>
+      </c>
+      <c r="K77" t="str">
+        <f>IFERROR(VLOOKUP(A77,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L77">
+        <f t="shared" si="3"/>
+        <v>2448</v>
+      </c>
+      <c r="M77" t="e">
+        <f>VLOOKUP(A77,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>31886</v>
       </c>
@@ -2817,11 +6026,28 @@
       <c r="H78" s="11">
         <v>0</v>
       </c>
-      <c r="I78" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I78" t="str">
+        <f>IFERROR(VLOOKUP(A78,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K78" t="str">
+        <f>IFERROR(VLOOKUP(A78,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L78">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M78" t="e">
+        <f>VLOOKUP(A78,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>9241</v>
       </c>
@@ -2840,11 +6066,28 @@
       <c r="H79" s="11">
         <v>1850</v>
       </c>
-      <c r="I79" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I79" t="str">
+        <f>IFERROR(VLOOKUP(A79,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="2"/>
+        <v>6200</v>
+      </c>
+      <c r="K79" t="str">
+        <f>IFERROR(VLOOKUP(A79,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L79">
+        <f t="shared" si="3"/>
+        <v>6200</v>
+      </c>
+      <c r="M79" t="e">
+        <f>VLOOKUP(A79,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>38178</v>
       </c>
@@ -2852,7 +6095,7 @@
         <v>74</v>
       </c>
       <c r="C80" s="4">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="F80" s="4">
         <v>63</v>
@@ -2863,11 +6106,28 @@
       <c r="H80" s="11">
         <v>20</v>
       </c>
-      <c r="I80" s="12">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I80">
+        <f>IFERROR(VLOOKUP(A80,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <f>IFERROR(VLOOKUP(A80,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>77</v>
+      </c>
+      <c r="L80">
+        <f t="shared" si="3"/>
+        <v>77</v>
+      </c>
+      <c r="M80">
+        <f>VLOOKUP(A80,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>35365</v>
       </c>
@@ -2886,11 +6146,28 @@
       <c r="H81" s="11">
         <v>0</v>
       </c>
-      <c r="I81" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I81" t="str">
+        <f>IFERROR(VLOOKUP(A81,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K81" t="str">
+        <f>IFERROR(VLOOKUP(A81,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L81">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M81" t="e">
+        <f>VLOOKUP(A81,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>30489</v>
       </c>
@@ -2909,11 +6186,28 @@
       <c r="H82" s="11">
         <v>-6.1329999999999991</v>
       </c>
-      <c r="I82" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I82" t="str">
+        <f>IFERROR(VLOOKUP(A82,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="2"/>
+        <v>12.52</v>
+      </c>
+      <c r="K82" t="str">
+        <f>IFERROR(VLOOKUP(A82,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L82">
+        <f t="shared" si="3"/>
+        <v>12.52</v>
+      </c>
+      <c r="M82" t="e">
+        <f>VLOOKUP(A82,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>32388</v>
       </c>
@@ -2932,11 +6226,28 @@
       <c r="H83" s="11">
         <v>0</v>
       </c>
-      <c r="I83" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I83" t="str">
+        <f>IFERROR(VLOOKUP(A83,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K83" t="str">
+        <f>IFERROR(VLOOKUP(A83,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L83">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M83" t="e">
+        <f>VLOOKUP(A83,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>29403</v>
       </c>
@@ -2955,11 +6266,28 @@
       <c r="H84" s="11">
         <v>2</v>
       </c>
-      <c r="I84" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I84" t="str">
+        <f>IFERROR(VLOOKUP(A84,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K84" t="str">
+        <f>IFERROR(VLOOKUP(A84,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L84">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M84" t="e">
+        <f>VLOOKUP(A84,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>36308</v>
       </c>
@@ -2978,11 +6306,28 @@
       <c r="H85" s="11">
         <v>0</v>
       </c>
-      <c r="I85" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I85" t="str">
+        <f>IFERROR(VLOOKUP(A85,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K85" t="str">
+        <f>IFERROR(VLOOKUP(A85,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L85">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M85" t="e">
+        <f>VLOOKUP(A85,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>29004</v>
       </c>
@@ -3001,11 +6346,28 @@
       <c r="H86" s="11">
         <v>1671</v>
       </c>
-      <c r="I86" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I86" t="str">
+        <f>IFERROR(VLOOKUP(A86,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="2"/>
+        <v>535</v>
+      </c>
+      <c r="K86" t="str">
+        <f>IFERROR(VLOOKUP(A86,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L86">
+        <f t="shared" si="3"/>
+        <v>535</v>
+      </c>
+      <c r="M86" t="e">
+        <f>VLOOKUP(A86,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>29003</v>
       </c>
@@ -3024,11 +6386,28 @@
       <c r="H87" s="11">
         <v>2205</v>
       </c>
-      <c r="I87" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I87" t="str">
+        <f>IFERROR(VLOOKUP(A87,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="K87" t="str">
+        <f>IFERROR(VLOOKUP(A87,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L87">
+        <f t="shared" si="3"/>
+        <v>1000</v>
+      </c>
+      <c r="M87" t="e">
+        <f>VLOOKUP(A87,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>29001</v>
       </c>
@@ -3047,11 +6426,28 @@
       <c r="H88" s="11">
         <v>653</v>
       </c>
-      <c r="I88" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I88" t="str">
+        <f>IFERROR(VLOOKUP(A88,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="2"/>
+        <v>398</v>
+      </c>
+      <c r="K88" t="str">
+        <f>IFERROR(VLOOKUP(A88,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L88">
+        <f t="shared" si="3"/>
+        <v>398</v>
+      </c>
+      <c r="M88" t="e">
+        <f>VLOOKUP(A88,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>38726</v>
       </c>
@@ -3070,11 +6466,28 @@
       <c r="H89" s="11">
         <v>212</v>
       </c>
-      <c r="I89" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I89" t="str">
+        <f>IFERROR(VLOOKUP(A89,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="K89" t="str">
+        <f>IFERROR(VLOOKUP(A89,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L89">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="M89" t="e">
+        <f>VLOOKUP(A89,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>29857</v>
       </c>
@@ -3093,11 +6506,28 @@
       <c r="H90" s="11">
         <v>33</v>
       </c>
-      <c r="I90" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I90" t="str">
+        <f>IFERROR(VLOOKUP(A90,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="K90" t="str">
+        <f>IFERROR(VLOOKUP(A90,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L90">
+        <f t="shared" si="3"/>
+        <v>242</v>
+      </c>
+      <c r="M90" t="e">
+        <f>VLOOKUP(A90,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>28999</v>
       </c>
@@ -3116,11 +6546,28 @@
       <c r="H91" s="11">
         <v>630</v>
       </c>
-      <c r="I91" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I91" t="str">
+        <f>IFERROR(VLOOKUP(A91,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="2"/>
+        <v>1048</v>
+      </c>
+      <c r="K91" t="str">
+        <f>IFERROR(VLOOKUP(A91,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L91">
+        <f t="shared" si="3"/>
+        <v>1048</v>
+      </c>
+      <c r="M91" t="e">
+        <f>VLOOKUP(A91,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>29000</v>
       </c>
@@ -3139,11 +6586,28 @@
       <c r="H92" s="11">
         <v>1437</v>
       </c>
-      <c r="I92" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I92" t="str">
+        <f>IFERROR(VLOOKUP(A92,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J92">
+        <f t="shared" si="2"/>
+        <v>1750</v>
+      </c>
+      <c r="K92" t="str">
+        <f>IFERROR(VLOOKUP(A92,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L92">
+        <f t="shared" si="3"/>
+        <v>1750</v>
+      </c>
+      <c r="M92" t="e">
+        <f>VLOOKUP(A92,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>29002</v>
       </c>
@@ -3162,11 +6626,28 @@
       <c r="H93" s="11">
         <v>2470</v>
       </c>
-      <c r="I93" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I93" t="str">
+        <f>IFERROR(VLOOKUP(A93,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J93">
+        <f t="shared" si="2"/>
+        <v>632</v>
+      </c>
+      <c r="K93" t="str">
+        <f>IFERROR(VLOOKUP(A93,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L93">
+        <f t="shared" si="3"/>
+        <v>632</v>
+      </c>
+      <c r="M93" t="e">
+        <f>VLOOKUP(A93,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>34607</v>
       </c>
@@ -3185,11 +6666,28 @@
       <c r="H94" s="11">
         <v>-10</v>
       </c>
-      <c r="I94" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I94" t="str">
+        <f>IFERROR(VLOOKUP(A94,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J94">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="K94" t="str">
+        <f>IFERROR(VLOOKUP(A94,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L94">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="M94" t="e">
+        <f>VLOOKUP(A94,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>39142</v>
       </c>
@@ -3197,7 +6695,7 @@
         <v>89</v>
       </c>
       <c r="C95" s="4">
-        <v>2.2999999999999998</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F95" s="4">
         <v>2.605</v>
@@ -3208,11 +6706,28 @@
       <c r="H95" s="11">
         <v>0.20300000000000029</v>
       </c>
-      <c r="I95" s="12">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I95">
+        <f>IFERROR(VLOOKUP(A95,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>1.7249999999999999</v>
+      </c>
+      <c r="J95">
+        <f t="shared" si="2"/>
+        <v>1.7249999999999999</v>
+      </c>
+      <c r="K95">
+        <f>IFERROR(VLOOKUP(A95,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>1.7249999999999999</v>
+      </c>
+      <c r="L95">
+        <f t="shared" si="3"/>
+        <v>1.7249999999999999</v>
+      </c>
+      <c r="M95">
+        <f>VLOOKUP(A95,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>32374</v>
       </c>
@@ -3231,11 +6746,28 @@
       <c r="H96" s="11">
         <v>13.9206</v>
       </c>
-      <c r="I96" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I96" t="str">
+        <f>IFERROR(VLOOKUP(A96,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J96">
+        <f t="shared" si="2"/>
+        <v>16.2</v>
+      </c>
+      <c r="K96" t="str">
+        <f>IFERROR(VLOOKUP(A96,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L96">
+        <f t="shared" si="3"/>
+        <v>16.2</v>
+      </c>
+      <c r="M96" t="e">
+        <f>VLOOKUP(A96,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>37709</v>
       </c>
@@ -3254,11 +6786,28 @@
       <c r="H97" s="11">
         <v>167</v>
       </c>
-      <c r="I97" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I97" t="str">
+        <f>IFERROR(VLOOKUP(A97,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J97">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K97" t="str">
+        <f>IFERROR(VLOOKUP(A97,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L97">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M97" t="e">
+        <f>VLOOKUP(A97,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>35205</v>
       </c>
@@ -3277,11 +6826,28 @@
       <c r="H98" s="11">
         <v>0</v>
       </c>
-      <c r="I98" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I98" t="str">
+        <f>IFERROR(VLOOKUP(A98,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J98">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K98" t="str">
+        <f>IFERROR(VLOOKUP(A98,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L98">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M98" t="e">
+        <f>VLOOKUP(A98,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>35740</v>
       </c>
@@ -3300,11 +6866,28 @@
       <c r="H99" s="11">
         <v>-160</v>
       </c>
-      <c r="I99" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I99" t="str">
+        <f>IFERROR(VLOOKUP(A99,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J99">
+        <f t="shared" si="2"/>
+        <v>230</v>
+      </c>
+      <c r="K99" t="str">
+        <f>IFERROR(VLOOKUP(A99,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L99">
+        <f t="shared" si="3"/>
+        <v>230</v>
+      </c>
+      <c r="M99" t="e">
+        <f>VLOOKUP(A99,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>38474</v>
       </c>
@@ -3323,11 +6906,28 @@
       <c r="H100" s="11">
         <v>0</v>
       </c>
-      <c r="I100" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I100" t="str">
+        <f>IFERROR(VLOOKUP(A100,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J100">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K100" t="str">
+        <f>IFERROR(VLOOKUP(A100,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L100">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M100" t="e">
+        <f>VLOOKUP(A100,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>38678</v>
       </c>
@@ -3346,11 +6946,28 @@
       <c r="H101" s="11">
         <v>0</v>
       </c>
-      <c r="I101" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I101" t="str">
+        <f>IFERROR(VLOOKUP(A101,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J101">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K101" t="str">
+        <f>IFERROR(VLOOKUP(A101,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L101">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M101" t="e">
+        <f>VLOOKUP(A101,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>35708</v>
       </c>
@@ -3369,11 +6986,28 @@
       <c r="H102" s="11">
         <v>-11.608000000000001</v>
       </c>
-      <c r="I102" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I102" t="str">
+        <f>IFERROR(VLOOKUP(A102,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J102">
+        <f t="shared" si="2"/>
+        <v>12.228</v>
+      </c>
+      <c r="K102" t="str">
+        <f>IFERROR(VLOOKUP(A102,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L102">
+        <f t="shared" si="3"/>
+        <v>12.228</v>
+      </c>
+      <c r="M102" t="e">
+        <f>VLOOKUP(A102,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>36083</v>
       </c>
@@ -3392,11 +7026,28 @@
       <c r="H103" s="11">
         <v>-3.5570000000000004</v>
       </c>
-      <c r="I103" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I103" t="str">
+        <f>IFERROR(VLOOKUP(A103,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J103">
+        <f t="shared" si="2"/>
+        <v>9.2949999999999999</v>
+      </c>
+      <c r="K103" t="str">
+        <f>IFERROR(VLOOKUP(A103,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L103">
+        <f t="shared" si="3"/>
+        <v>9.2949999999999999</v>
+      </c>
+      <c r="M103" t="e">
+        <f>VLOOKUP(A103,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>36084</v>
       </c>
@@ -3415,11 +7066,28 @@
       <c r="H104" s="11">
         <v>-2</v>
       </c>
-      <c r="I104" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I104" t="str">
+        <f>IFERROR(VLOOKUP(A104,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J104">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="K104" t="str">
+        <f>IFERROR(VLOOKUP(A104,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L104">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="M104" t="e">
+        <f>VLOOKUP(A104,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>34862</v>
       </c>
@@ -3438,11 +7106,28 @@
       <c r="H105" s="11">
         <v>17</v>
       </c>
-      <c r="I105" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I105" t="str">
+        <f>IFERROR(VLOOKUP(A105,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J105">
+        <f t="shared" si="2"/>
+        <v>98</v>
+      </c>
+      <c r="K105" t="str">
+        <f>IFERROR(VLOOKUP(A105,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L105">
+        <f t="shared" si="3"/>
+        <v>98</v>
+      </c>
+      <c r="M105" t="e">
+        <f>VLOOKUP(A105,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>38460</v>
       </c>
@@ -3461,11 +7146,28 @@
       <c r="H106" s="11">
         <v>0</v>
       </c>
-      <c r="I106" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I106" t="str">
+        <f>IFERROR(VLOOKUP(A106,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J106">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K106" t="str">
+        <f>IFERROR(VLOOKUP(A106,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L106">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M106" t="e">
+        <f>VLOOKUP(A106,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>34638</v>
       </c>
@@ -3484,11 +7186,28 @@
       <c r="H107" s="11">
         <v>3.2130000000000001</v>
       </c>
-      <c r="I107" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I107" t="str">
+        <f>IFERROR(VLOOKUP(A107,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J107">
+        <f t="shared" si="2"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="K107" t="str">
+        <f>IFERROR(VLOOKUP(A107,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L107">
+        <f t="shared" si="3"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M107" t="e">
+        <f>VLOOKUP(A107,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>39190</v>
       </c>
@@ -3507,11 +7226,28 @@
       <c r="H108" s="11">
         <v>0</v>
       </c>
-      <c r="I108" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I108" t="str">
+        <f>IFERROR(VLOOKUP(A108,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J108">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K108" t="str">
+        <f>IFERROR(VLOOKUP(A108,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M108" t="e">
+        <f>VLOOKUP(A108,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>35562</v>
       </c>
@@ -3530,11 +7266,28 @@
       <c r="H109" s="11">
         <v>9.75</v>
       </c>
-      <c r="I109" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I109" t="str">
+        <f>IFERROR(VLOOKUP(A109,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J109">
+        <f t="shared" si="2"/>
+        <v>0.745</v>
+      </c>
+      <c r="K109" t="str">
+        <f>IFERROR(VLOOKUP(A109,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L109">
+        <f t="shared" si="3"/>
+        <v>0.745</v>
+      </c>
+      <c r="M109" t="e">
+        <f>VLOOKUP(A109,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>38995</v>
       </c>
@@ -3553,11 +7306,28 @@
       <c r="H110" s="11">
         <v>0</v>
       </c>
-      <c r="I110" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I110" t="str">
+        <f>IFERROR(VLOOKUP(A110,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J110">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K110" t="str">
+        <f>IFERROR(VLOOKUP(A110,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L110">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M110" t="e">
+        <f>VLOOKUP(A110,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>21288</v>
       </c>
@@ -3576,11 +7346,28 @@
       <c r="H111" s="11">
         <v>-8.5249999999999986</v>
       </c>
-      <c r="I111" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I111" t="str">
+        <f>IFERROR(VLOOKUP(A111,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J111">
+        <f t="shared" si="2"/>
+        <v>21.05</v>
+      </c>
+      <c r="K111" t="str">
+        <f>IFERROR(VLOOKUP(A111,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L111">
+        <f t="shared" si="3"/>
+        <v>21.05</v>
+      </c>
+      <c r="M111" t="e">
+        <f>VLOOKUP(A111,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>35407</v>
       </c>
@@ -3599,11 +7386,28 @@
       <c r="H112" s="11">
         <v>3.9880000000000004</v>
       </c>
-      <c r="I112" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I112" t="str">
+        <f>IFERROR(VLOOKUP(A112,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J112">
+        <f t="shared" si="2"/>
+        <v>2.2869999999999999</v>
+      </c>
+      <c r="K112" t="str">
+        <f>IFERROR(VLOOKUP(A112,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L112">
+        <f t="shared" si="3"/>
+        <v>2.2869999999999999</v>
+      </c>
+      <c r="M112" t="e">
+        <f>VLOOKUP(A112,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>35408</v>
       </c>
@@ -3622,11 +7426,28 @@
       <c r="H113" s="11">
         <v>1287</v>
       </c>
-      <c r="I113" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I113" t="str">
+        <f>IFERROR(VLOOKUP(A113,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J113">
+        <f t="shared" si="2"/>
+        <v>3184</v>
+      </c>
+      <c r="K113" t="str">
+        <f>IFERROR(VLOOKUP(A113,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L113">
+        <f t="shared" si="3"/>
+        <v>3184</v>
+      </c>
+      <c r="M113" t="e">
+        <f>VLOOKUP(A113,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>38662</v>
       </c>
@@ -3645,11 +7466,28 @@
       <c r="H114" s="11">
         <v>0</v>
       </c>
-      <c r="I114" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I114" t="str">
+        <f>IFERROR(VLOOKUP(A114,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J114">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K114" t="str">
+        <f>IFERROR(VLOOKUP(A114,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L114">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M114" t="e">
+        <f>VLOOKUP(A114,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>35912</v>
       </c>
@@ -3668,11 +7506,28 @@
       <c r="H115" s="11">
         <v>1.7300000000000004</v>
       </c>
-      <c r="I115" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I115" t="str">
+        <f>IFERROR(VLOOKUP(A115,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J115">
+        <f t="shared" si="2"/>
+        <v>3.9699999999999998</v>
+      </c>
+      <c r="K115" t="str">
+        <f>IFERROR(VLOOKUP(A115,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L115">
+        <f t="shared" si="3"/>
+        <v>3.9699999999999998</v>
+      </c>
+      <c r="M115" t="e">
+        <f>VLOOKUP(A115,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>20754</v>
       </c>
@@ -3691,11 +7546,28 @@
       <c r="H116" s="11">
         <v>20.437999999999999</v>
       </c>
-      <c r="I116" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I116" t="str">
+        <f>IFERROR(VLOOKUP(A116,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J116">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K116" t="str">
+        <f>IFERROR(VLOOKUP(A116,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L116">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M116" t="e">
+        <f>VLOOKUP(A116,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>35194</v>
       </c>
@@ -3714,11 +7586,28 @@
       <c r="H117" s="11">
         <v>0</v>
       </c>
-      <c r="I117" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I117" t="str">
+        <f>IFERROR(VLOOKUP(A117,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J117">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K117" t="str">
+        <f>IFERROR(VLOOKUP(A117,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L117">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M117" t="e">
+        <f>VLOOKUP(A117,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>13363</v>
       </c>
@@ -3737,11 +7626,28 @@
       <c r="H118" s="11">
         <v>-2.8279999999999994</v>
       </c>
-      <c r="I118" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I118" t="str">
+        <f>IFERROR(VLOOKUP(A118,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J118">
+        <f t="shared" si="2"/>
+        <v>5.6079999999999997</v>
+      </c>
+      <c r="K118" t="str">
+        <f>IFERROR(VLOOKUP(A118,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L118">
+        <f t="shared" si="3"/>
+        <v>5.6079999999999997</v>
+      </c>
+      <c r="M118" t="e">
+        <f>VLOOKUP(A118,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>21215</v>
       </c>
@@ -3760,11 +7666,28 @@
       <c r="H119" s="11">
         <v>5.3000000000000824E-2</v>
       </c>
-      <c r="I119" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I119" t="str">
+        <f>IFERROR(VLOOKUP(A119,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J119">
+        <f t="shared" si="2"/>
+        <v>9.3019999999999996</v>
+      </c>
+      <c r="K119" t="str">
+        <f>IFERROR(VLOOKUP(A119,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L119">
+        <f t="shared" si="3"/>
+        <v>9.3019999999999996</v>
+      </c>
+      <c r="M119" t="e">
+        <f>VLOOKUP(A119,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>39041</v>
       </c>
@@ -3783,11 +7706,28 @@
       <c r="H120" s="11">
         <v>0</v>
       </c>
-      <c r="I120" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I120" t="str">
+        <f>IFERROR(VLOOKUP(A120,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J120">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K120" t="str">
+        <f>IFERROR(VLOOKUP(A120,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L120">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M120" t="e">
+        <f>VLOOKUP(A120,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>35103</v>
       </c>
@@ -3795,7 +7735,7 @@
         <v>115</v>
       </c>
       <c r="C121" s="4">
-        <v>638</v>
+        <v>956</v>
       </c>
       <c r="F121" s="4">
         <v>269</v>
@@ -3806,11 +7746,27 @@
       <c r="H121" s="11">
         <v>169</v>
       </c>
-      <c r="I121" s="12">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I121">
+        <f>IFERROR(VLOOKUP(A121,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>1197</v>
+      </c>
+      <c r="J121">
+        <f t="shared" si="2"/>
+        <v>1197</v>
+      </c>
+      <c r="K121" t="str">
+        <f>IFERROR(VLOOKUP(A121,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <f>VLOOKUP(A121,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>956</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="7">
         <v>34840</v>
       </c>
@@ -3818,7 +7774,7 @@
         <v>165</v>
       </c>
       <c r="C122" s="4">
-        <v>0</v>
+        <v>956</v>
       </c>
       <c r="F122" s="4">
         <v>0</v>
@@ -3829,11 +7785,28 @@
       <c r="H122" s="11">
         <v>0</v>
       </c>
-      <c r="I122" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I122" t="str">
+        <f>IFERROR(VLOOKUP(A122,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J122">
+        <f t="shared" si="2"/>
+        <v>956</v>
+      </c>
+      <c r="K122">
+        <f>IFERROR(VLOOKUP(A122,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>546</v>
+      </c>
+      <c r="L122">
+        <f t="shared" si="3"/>
+        <v>546</v>
+      </c>
+      <c r="M122" t="e">
+        <f>VLOOKUP(A122,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>39141</v>
       </c>
@@ -3852,11 +7825,28 @@
       <c r="H123" s="11">
         <v>141</v>
       </c>
-      <c r="I123" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I123" t="str">
+        <f>IFERROR(VLOOKUP(A123,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J123">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K123" t="str">
+        <f>IFERROR(VLOOKUP(A123,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L123">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M123" t="e">
+        <f>VLOOKUP(A123,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>38585</v>
       </c>
@@ -3864,7 +7854,7 @@
         <v>117</v>
       </c>
       <c r="C124" s="4">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="F124" s="4">
         <v>118</v>
@@ -3875,11 +7865,28 @@
       <c r="H124" s="11">
         <v>5</v>
       </c>
-      <c r="I124" s="12">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I124">
+        <f>IFERROR(VLOOKUP(A124,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>80</v>
+      </c>
+      <c r="J124">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="K124">
+        <f>IFERROR(VLOOKUP(A124,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>83</v>
+      </c>
+      <c r="L124">
+        <f t="shared" si="3"/>
+        <v>83</v>
+      </c>
+      <c r="M124">
+        <f>VLOOKUP(A124,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="7">
         <v>34459</v>
       </c>
@@ -3887,7 +7894,7 @@
         <v>164</v>
       </c>
       <c r="C125" s="4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F125" s="4" t="e">
         <v>#N/A</v>
@@ -3898,11 +7905,27 @@
       <c r="H125" s="11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="I125" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I125" t="str">
+        <f>IFERROR(VLOOKUP(A125,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J125">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="K125" t="str">
+        <f>IFERROR(VLOOKUP(A125,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125" t="e">
+        <f>VLOOKUP(A125,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>36252</v>
       </c>
@@ -3910,7 +7933,7 @@
         <v>118</v>
       </c>
       <c r="C126" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="4">
         <v>115</v>
@@ -3921,11 +7944,28 @@
       <c r="H126" s="11">
         <v>90</v>
       </c>
-      <c r="I126" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I126">
+        <f>IFERROR(VLOOKUP(A126,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>345</v>
+      </c>
+      <c r="J126">
+        <f t="shared" si="2"/>
+        <v>345</v>
+      </c>
+      <c r="K126">
+        <f>IFERROR(VLOOKUP(A126,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>194</v>
+      </c>
+      <c r="L126">
+        <f t="shared" si="3"/>
+        <v>194</v>
+      </c>
+      <c r="M126">
+        <f>VLOOKUP(A126,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>34754</v>
       </c>
@@ -3933,7 +7973,7 @@
         <v>119</v>
       </c>
       <c r="C127" s="4">
-        <v>317</v>
+        <v>456</v>
       </c>
       <c r="F127" s="4">
         <v>337</v>
@@ -3944,11 +7984,28 @@
       <c r="H127" s="11">
         <v>245</v>
       </c>
-      <c r="I127" s="12">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I127">
+        <f>IFERROR(VLOOKUP(A127,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>375</v>
+      </c>
+      <c r="J127">
+        <f t="shared" si="2"/>
+        <v>375</v>
+      </c>
+      <c r="K127">
+        <f>IFERROR(VLOOKUP(A127,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>159</v>
+      </c>
+      <c r="L127">
+        <f t="shared" si="3"/>
+        <v>159</v>
+      </c>
+      <c r="M127">
+        <f>VLOOKUP(A127,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>456</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>32605</v>
       </c>
@@ -3967,11 +8024,28 @@
       <c r="H128" s="11">
         <v>2008</v>
       </c>
-      <c r="I128" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I128" t="str">
+        <f>IFERROR(VLOOKUP(A128,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J128">
+        <f t="shared" si="2"/>
+        <v>3870</v>
+      </c>
+      <c r="K128" t="str">
+        <f>IFERROR(VLOOKUP(A128,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L128">
+        <f t="shared" si="3"/>
+        <v>3870</v>
+      </c>
+      <c r="M128" t="e">
+        <f>VLOOKUP(A128,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>32375</v>
       </c>
@@ -3990,11 +8064,28 @@
       <c r="H129" s="11">
         <v>-4524</v>
       </c>
-      <c r="I129" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I129" t="str">
+        <f>IFERROR(VLOOKUP(A129,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J129">
+        <f t="shared" si="2"/>
+        <v>6249</v>
+      </c>
+      <c r="K129" t="str">
+        <f>IFERROR(VLOOKUP(A129,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L129">
+        <f t="shared" si="3"/>
+        <v>6249</v>
+      </c>
+      <c r="M129" t="e">
+        <f>VLOOKUP(A129,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>772</v>
       </c>
@@ -4013,11 +8104,28 @@
       <c r="H130" s="11">
         <v>-2</v>
       </c>
-      <c r="I130" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I130" t="str">
+        <f>IFERROR(VLOOKUP(A130,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J130">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="K130" t="str">
+        <f>IFERROR(VLOOKUP(A130,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L130">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="M130" t="e">
+        <f>VLOOKUP(A130,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>9442</v>
       </c>
@@ -4036,11 +8144,28 @@
       <c r="H131" s="11">
         <v>0</v>
       </c>
-      <c r="I131" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I131" t="str">
+        <f>IFERROR(VLOOKUP(A131,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J131">
+        <f t="shared" ref="J131:J169" si="4">IF(I131="NA",C131,I131)</f>
+        <v>0</v>
+      </c>
+      <c r="K131" t="str">
+        <f>IFERROR(VLOOKUP(A131,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L131">
+        <f t="shared" ref="L131:L169" si="5">IF(K131="NAO",C131,K131)</f>
+        <v>0</v>
+      </c>
+      <c r="M131" t="e">
+        <f>VLOOKUP(A131,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>15190</v>
       </c>
@@ -4059,11 +8184,28 @@
       <c r="H132" s="11">
         <v>7</v>
       </c>
-      <c r="I132" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I132" t="str">
+        <f>IFERROR(VLOOKUP(A132,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J132">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="K132" t="str">
+        <f>IFERROR(VLOOKUP(A132,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L132">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="M132" t="e">
+        <f>VLOOKUP(A132,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>9096</v>
       </c>
@@ -4071,7 +8213,7 @@
         <v>125</v>
       </c>
       <c r="C133" s="4">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F133" s="4">
         <v>0</v>
@@ -4082,11 +8224,28 @@
       <c r="H133" s="11">
         <v>-55</v>
       </c>
-      <c r="I133" s="12">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I133">
+        <f>IFERROR(VLOOKUP(A133,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <f>IFERROR(VLOOKUP(A133,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>53</v>
+      </c>
+      <c r="L133">
+        <f t="shared" si="5"/>
+        <v>53</v>
+      </c>
+      <c r="M133">
+        <f>VLOOKUP(A133,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>9274</v>
       </c>
@@ -4094,7 +8253,7 @@
         <v>126</v>
       </c>
       <c r="C134" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F134" s="4">
         <v>52</v>
@@ -4105,11 +8264,28 @@
       <c r="H134" s="11">
         <v>52</v>
       </c>
-      <c r="I134" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I134">
+        <f>IFERROR(VLOOKUP(A134,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <f>IFERROR(VLOOKUP(A134,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>18</v>
+      </c>
+      <c r="L134">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="M134">
+        <f>VLOOKUP(A134,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>35083</v>
       </c>
@@ -4128,11 +8304,28 @@
       <c r="H135" s="11">
         <v>0.10999999999999999</v>
       </c>
-      <c r="I135" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I135" t="str">
+        <f>IFERROR(VLOOKUP(A135,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J135">
+        <f t="shared" si="4"/>
+        <v>0.125</v>
+      </c>
+      <c r="K135" t="str">
+        <f>IFERROR(VLOOKUP(A135,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L135">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="M135" t="e">
+        <f>VLOOKUP(A135,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>38839</v>
       </c>
@@ -4151,11 +8344,28 @@
       <c r="H136" s="11">
         <v>0</v>
       </c>
-      <c r="I136" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I136" t="str">
+        <f>IFERROR(VLOOKUP(A136,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J136">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K136" t="str">
+        <f>IFERROR(VLOOKUP(A136,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L136">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M136" t="e">
+        <f>VLOOKUP(A136,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>35572</v>
       </c>
@@ -4174,11 +8384,28 @@
       <c r="H137" s="11">
         <v>-5</v>
       </c>
-      <c r="I137" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I137" t="str">
+        <f>IFERROR(VLOOKUP(A137,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J137">
+        <f t="shared" si="4"/>
+        <v>350</v>
+      </c>
+      <c r="K137" t="str">
+        <f>IFERROR(VLOOKUP(A137,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L137">
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+      <c r="M137" t="e">
+        <f>VLOOKUP(A137,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>35619</v>
       </c>
@@ -4186,7 +8413,7 @@
         <v>130</v>
       </c>
       <c r="C138" s="4">
-        <v>1118</v>
+        <v>3454</v>
       </c>
       <c r="F138" s="4">
         <v>1994</v>
@@ -4197,11 +8424,27 @@
       <c r="H138" s="11">
         <v>406</v>
       </c>
-      <c r="I138" s="12">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I138">
+        <f>IFERROR(VLOOKUP(A138,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>2304</v>
+      </c>
+      <c r="J138">
+        <f t="shared" si="4"/>
+        <v>2304</v>
+      </c>
+      <c r="K138" t="str">
+        <f>IFERROR(VLOOKUP(A138,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <f>VLOOKUP(A138,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>3454</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="7">
         <v>35610</v>
       </c>
@@ -4209,7 +8452,7 @@
         <v>166</v>
       </c>
       <c r="C139" s="4">
-        <v>0</v>
+        <v>3454</v>
       </c>
       <c r="F139" s="4">
         <v>0</v>
@@ -4220,11 +8463,28 @@
       <c r="H139" s="11">
         <v>0</v>
       </c>
-      <c r="I139" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I139" t="str">
+        <f>IFERROR(VLOOKUP(A139,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J139">
+        <f t="shared" si="4"/>
+        <v>3454</v>
+      </c>
+      <c r="K139">
+        <f>IFERROR(VLOOKUP(A139,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>1824</v>
+      </c>
+      <c r="L139">
+        <f t="shared" si="5"/>
+        <v>1824</v>
+      </c>
+      <c r="M139" t="e">
+        <f>VLOOKUP(A139,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>38141</v>
       </c>
@@ -4243,11 +8503,28 @@
       <c r="H140" s="11">
         <v>0</v>
       </c>
-      <c r="I140" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I140" t="str">
+        <f>IFERROR(VLOOKUP(A140,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K140" t="str">
+        <f>IFERROR(VLOOKUP(A140,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L140">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M140" t="e">
+        <f>VLOOKUP(A140,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>21671</v>
       </c>
@@ -4266,11 +8543,28 @@
       <c r="H141" s="11">
         <v>-205</v>
       </c>
-      <c r="I141" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I141" t="str">
+        <f>IFERROR(VLOOKUP(A141,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J141">
+        <f t="shared" si="4"/>
+        <v>205</v>
+      </c>
+      <c r="K141" t="str">
+        <f>IFERROR(VLOOKUP(A141,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L141">
+        <f t="shared" si="5"/>
+        <v>205</v>
+      </c>
+      <c r="M141" t="e">
+        <f>VLOOKUP(A141,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>33345</v>
       </c>
@@ -4289,11 +8583,28 @@
       <c r="H142" s="11">
         <v>0</v>
       </c>
-      <c r="I142" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I142" t="str">
+        <f>IFERROR(VLOOKUP(A142,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J142">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K142" t="str">
+        <f>IFERROR(VLOOKUP(A142,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L142">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M142" t="e">
+        <f>VLOOKUP(A142,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>32997</v>
       </c>
@@ -4312,11 +8623,28 @@
       <c r="H143" s="11">
         <v>33</v>
       </c>
-      <c r="I143" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I143" t="str">
+        <f>IFERROR(VLOOKUP(A143,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J143">
+        <f t="shared" si="4"/>
+        <v>42</v>
+      </c>
+      <c r="K143" t="str">
+        <f>IFERROR(VLOOKUP(A143,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L143">
+        <f t="shared" si="5"/>
+        <v>42</v>
+      </c>
+      <c r="M143" t="e">
+        <f>VLOOKUP(A143,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>35835</v>
       </c>
@@ -4335,11 +8663,28 @@
       <c r="H144" s="11">
         <v>-22</v>
       </c>
-      <c r="I144" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I144" t="str">
+        <f>IFERROR(VLOOKUP(A144,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J144">
+        <f t="shared" si="4"/>
+        <v>190</v>
+      </c>
+      <c r="K144" t="str">
+        <f>IFERROR(VLOOKUP(A144,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L144">
+        <f t="shared" si="5"/>
+        <v>190</v>
+      </c>
+      <c r="M144" t="e">
+        <f>VLOOKUP(A144,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>23188</v>
       </c>
@@ -4358,11 +8703,28 @@
       <c r="H145" s="11">
         <v>745</v>
       </c>
-      <c r="I145" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I145" t="str">
+        <f>IFERROR(VLOOKUP(A145,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J145">
+        <f t="shared" si="4"/>
+        <v>545</v>
+      </c>
+      <c r="K145" t="str">
+        <f>IFERROR(VLOOKUP(A145,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L145">
+        <f t="shared" si="5"/>
+        <v>545</v>
+      </c>
+      <c r="M145" t="e">
+        <f>VLOOKUP(A145,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>37811</v>
       </c>
@@ -4381,11 +8743,28 @@
       <c r="H146" s="11">
         <v>0</v>
       </c>
-      <c r="I146" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I146" t="str">
+        <f>IFERROR(VLOOKUP(A146,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J146">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K146" t="str">
+        <f>IFERROR(VLOOKUP(A146,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L146">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M146" t="e">
+        <f>VLOOKUP(A146,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>35505</v>
       </c>
@@ -4404,11 +8783,28 @@
       <c r="H147" s="11">
         <v>-58</v>
       </c>
-      <c r="I147" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I147" t="str">
+        <f>IFERROR(VLOOKUP(A147,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J147">
+        <f t="shared" si="4"/>
+        <v>158</v>
+      </c>
+      <c r="K147" t="str">
+        <f>IFERROR(VLOOKUP(A147,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L147">
+        <f t="shared" si="5"/>
+        <v>158</v>
+      </c>
+      <c r="M147" t="e">
+        <f>VLOOKUP(A147,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>36109</v>
       </c>
@@ -4427,11 +8823,28 @@
       <c r="H148" s="11">
         <v>0</v>
       </c>
-      <c r="I148" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I148" t="str">
+        <f>IFERROR(VLOOKUP(A148,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J148">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K148" t="str">
+        <f>IFERROR(VLOOKUP(A148,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L148">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M148" t="e">
+        <f>VLOOKUP(A148,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>19555</v>
       </c>
@@ -4450,11 +8863,28 @@
       <c r="H149" s="11">
         <v>1337</v>
       </c>
-      <c r="I149" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I149" t="str">
+        <f>IFERROR(VLOOKUP(A149,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J149">
+        <f t="shared" si="4"/>
+        <v>258</v>
+      </c>
+      <c r="K149" t="str">
+        <f>IFERROR(VLOOKUP(A149,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L149">
+        <f t="shared" si="5"/>
+        <v>258</v>
+      </c>
+      <c r="M149" t="e">
+        <f>VLOOKUP(A149,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>19556</v>
       </c>
@@ -4473,11 +8903,28 @@
       <c r="H150" s="11">
         <v>0</v>
       </c>
-      <c r="I150" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I150" t="str">
+        <f>IFERROR(VLOOKUP(A150,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J150">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K150" t="str">
+        <f>IFERROR(VLOOKUP(A150,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L150">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M150" t="e">
+        <f>VLOOKUP(A150,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>19557</v>
       </c>
@@ -4496,11 +8943,28 @@
       <c r="H151" s="11">
         <v>226</v>
       </c>
-      <c r="I151" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I151" t="str">
+        <f>IFERROR(VLOOKUP(A151,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J151">
+        <f t="shared" si="4"/>
+        <v>274</v>
+      </c>
+      <c r="K151" t="str">
+        <f>IFERROR(VLOOKUP(A151,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L151">
+        <f t="shared" si="5"/>
+        <v>274</v>
+      </c>
+      <c r="M151" t="e">
+        <f>VLOOKUP(A151,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>10947</v>
       </c>
@@ -4519,11 +8983,28 @@
       <c r="H152" s="11">
         <v>0.38500000000000006</v>
       </c>
-      <c r="I152" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I152" t="str">
+        <f>IFERROR(VLOOKUP(A152,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J152">
+        <f t="shared" si="4"/>
+        <v>0.3</v>
+      </c>
+      <c r="K152" t="str">
+        <f>IFERROR(VLOOKUP(A152,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L152">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="M152" t="e">
+        <f>VLOOKUP(A152,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>33290</v>
       </c>
@@ -4542,11 +9023,28 @@
       <c r="H153" s="11">
         <v>-908</v>
       </c>
-      <c r="I153" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I153" t="str">
+        <f>IFERROR(VLOOKUP(A153,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J153">
+        <f t="shared" si="4"/>
+        <v>2500</v>
+      </c>
+      <c r="K153" t="str">
+        <f>IFERROR(VLOOKUP(A153,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L153">
+        <f t="shared" si="5"/>
+        <v>2500</v>
+      </c>
+      <c r="M153" t="e">
+        <f>VLOOKUP(A153,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>35144</v>
       </c>
@@ -4565,11 +9063,28 @@
       <c r="H154" s="11">
         <v>93</v>
       </c>
-      <c r="I154" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I154" t="str">
+        <f>IFERROR(VLOOKUP(A154,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J154">
+        <f t="shared" si="4"/>
+        <v>1305</v>
+      </c>
+      <c r="K154" t="str">
+        <f>IFERROR(VLOOKUP(A154,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L154">
+        <f t="shared" si="5"/>
+        <v>1305</v>
+      </c>
+      <c r="M154" t="e">
+        <f>VLOOKUP(A154,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>2248</v>
       </c>
@@ -4588,11 +9103,28 @@
       <c r="H155" s="11">
         <v>12</v>
       </c>
-      <c r="I155" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I155" t="str">
+        <f>IFERROR(VLOOKUP(A155,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J155">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="K155" t="str">
+        <f>IFERROR(VLOOKUP(A155,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L155">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="M155" t="e">
+        <f>VLOOKUP(A155,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>7431</v>
       </c>
@@ -4611,11 +9143,28 @@
       <c r="H156" s="11">
         <v>23</v>
       </c>
-      <c r="I156" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I156" t="str">
+        <f>IFERROR(VLOOKUP(A156,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J156">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="K156" t="str">
+        <f>IFERROR(VLOOKUP(A156,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L156">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="M156" t="e">
+        <f>VLOOKUP(A156,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>35047</v>
       </c>
@@ -4623,7 +9172,7 @@
         <v>148</v>
       </c>
       <c r="C157" s="4">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F157" s="4">
         <v>22</v>
@@ -4634,11 +9183,28 @@
       <c r="H157" s="11">
         <v>-2</v>
       </c>
-      <c r="I157" s="12">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I157">
+        <f>IFERROR(VLOOKUP(A157,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <f>IFERROR(VLOOKUP(A157,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>33</v>
+      </c>
+      <c r="L157">
+        <f t="shared" si="5"/>
+        <v>33</v>
+      </c>
+      <c r="M157">
+        <f>VLOOKUP(A157,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>35959</v>
       </c>
@@ -4646,7 +9212,7 @@
         <v>149</v>
       </c>
       <c r="C158" s="4">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F158" s="4">
         <v>23</v>
@@ -4657,11 +9223,28 @@
       <c r="H158" s="11">
         <v>-1</v>
       </c>
-      <c r="I158" s="12">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I158">
+        <f>IFERROR(VLOOKUP(A158,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <f>IFERROR(VLOOKUP(A158,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>34</v>
+      </c>
+      <c r="L158">
+        <f t="shared" si="5"/>
+        <v>34</v>
+      </c>
+      <c r="M158">
+        <f>VLOOKUP(A158,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>35046</v>
       </c>
@@ -4669,7 +9252,7 @@
         <v>150</v>
       </c>
       <c r="C159" s="4">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F159" s="4">
         <v>10</v>
@@ -4680,11 +9263,28 @@
       <c r="H159" s="11">
         <v>9</v>
       </c>
-      <c r="I159" s="12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I159">
+        <f>IFERROR(VLOOKUP(A159,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>0</v>
+      </c>
+      <c r="J159">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <f>IFERROR(VLOOKUP(A159,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>3</v>
+      </c>
+      <c r="L159">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="M159">
+        <f>VLOOKUP(A159,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>33128</v>
       </c>
@@ -4703,11 +9303,28 @@
       <c r="H160" s="11">
         <v>92</v>
       </c>
-      <c r="I160" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I160" t="str">
+        <f>IFERROR(VLOOKUP(A160,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J160">
+        <f t="shared" si="4"/>
+        <v>758</v>
+      </c>
+      <c r="K160" t="str">
+        <f>IFERROR(VLOOKUP(A160,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L160">
+        <f t="shared" si="5"/>
+        <v>758</v>
+      </c>
+      <c r="M160" t="e">
+        <f>VLOOKUP(A160,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>22156</v>
       </c>
@@ -4726,11 +9343,28 @@
       <c r="H161" s="11">
         <v>19</v>
       </c>
-      <c r="I161" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I161" t="str">
+        <f>IFERROR(VLOOKUP(A161,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J161">
+        <f t="shared" si="4"/>
+        <v>245</v>
+      </c>
+      <c r="K161" t="str">
+        <f>IFERROR(VLOOKUP(A161,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L161">
+        <f t="shared" si="5"/>
+        <v>245</v>
+      </c>
+      <c r="M161" t="e">
+        <f>VLOOKUP(A161,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>31193</v>
       </c>
@@ -4749,11 +9383,28 @@
       <c r="H162" s="11">
         <v>0</v>
       </c>
-      <c r="I162" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I162" t="str">
+        <f>IFERROR(VLOOKUP(A162,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J162">
+        <f t="shared" si="4"/>
+        <v>250</v>
+      </c>
+      <c r="K162" t="str">
+        <f>IFERROR(VLOOKUP(A162,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L162">
+        <f t="shared" si="5"/>
+        <v>250</v>
+      </c>
+      <c r="M162" t="e">
+        <f>VLOOKUP(A162,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>31439</v>
       </c>
@@ -4772,11 +9423,28 @@
       <c r="H163" s="11">
         <v>-42</v>
       </c>
-      <c r="I163" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I163" t="str">
+        <f>IFERROR(VLOOKUP(A163,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J163">
+        <f t="shared" si="4"/>
+        <v>1642</v>
+      </c>
+      <c r="K163" t="str">
+        <f>IFERROR(VLOOKUP(A163,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L163">
+        <f t="shared" si="5"/>
+        <v>1642</v>
+      </c>
+      <c r="M163" t="e">
+        <f>VLOOKUP(A163,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>34600</v>
       </c>
@@ -4795,11 +9463,28 @@
       <c r="H164" s="11">
         <v>-905</v>
       </c>
-      <c r="I164" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I164" t="str">
+        <f>IFERROR(VLOOKUP(A164,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J164">
+        <f t="shared" si="4"/>
+        <v>930</v>
+      </c>
+      <c r="K164" t="str">
+        <f>IFERROR(VLOOKUP(A164,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L164">
+        <f t="shared" si="5"/>
+        <v>930</v>
+      </c>
+      <c r="M164" t="e">
+        <f>VLOOKUP(A164,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>34741</v>
       </c>
@@ -4818,11 +9503,28 @@
       <c r="H165" s="11">
         <v>0</v>
       </c>
-      <c r="I165" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I165" t="str">
+        <f>IFERROR(VLOOKUP(A165,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J165">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K165" t="str">
+        <f>IFERROR(VLOOKUP(A165,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M165" t="e">
+        <f>VLOOKUP(A165,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>36206</v>
       </c>
@@ -4830,7 +9532,7 @@
         <v>157</v>
       </c>
       <c r="C166" s="4">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="F166" s="4">
         <v>11</v>
@@ -4841,11 +9543,28 @@
       <c r="H166" s="11">
         <v>11</v>
       </c>
-      <c r="I166" s="12">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I166">
+        <f>IFERROR(VLOOKUP(A166,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>39</v>
+      </c>
+      <c r="J166">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+      <c r="K166">
+        <f>IFERROR(VLOOKUP(A166,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>25</v>
+      </c>
+      <c r="L166">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="M166">
+        <f>VLOOKUP(A166,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="7">
         <v>28451</v>
       </c>
@@ -4853,7 +9572,7 @@
         <v>163</v>
       </c>
       <c r="C167" s="4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F167" s="4">
         <v>0</v>
@@ -4864,11 +9583,27 @@
       <c r="H167" s="11">
         <v>0</v>
       </c>
-      <c r="I167" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I167" t="str">
+        <f>IFERROR(VLOOKUP(A167,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J167">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="K167" t="str">
+        <f>IFERROR(VLOOKUP(A167,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167" t="e">
+        <f>VLOOKUP(A167,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>19909</v>
       </c>
@@ -4887,11 +9622,28 @@
       <c r="H168" s="11">
         <v>0.79999999999999982</v>
       </c>
-      <c r="I168" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I168" t="str">
+        <f>IFERROR(VLOOKUP(A168,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J168">
+        <f t="shared" si="4"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K168" t="str">
+        <f>IFERROR(VLOOKUP(A168,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L168">
+        <f t="shared" si="5"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M168" t="e">
+        <f>VLOOKUP(A168,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>35219</v>
       </c>
@@ -4910,8 +9662,25 @@
       <c r="H169" s="11">
         <v>0</v>
       </c>
-      <c r="I169" t="s">
-        <v>171</v>
+      <c r="I169" t="str">
+        <f>IFERROR(VLOOKUP(A169,[1]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"NA")</f>
+        <v>NA</v>
+      </c>
+      <c r="J169">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K169" t="str">
+        <f>IFERROR(VLOOKUP(A169,[2]CONTAGEM_DIARIA_JUL25!$B:$M,12,0),"nao")</f>
+        <v>nao</v>
+      </c>
+      <c r="L169">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M169" t="e">
+        <f>VLOOKUP(A169,[3]CONTAGEM_DIARIA_JUL25!$B:$M,12,0)</f>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>

--- a/BKQBF_TAB-8.xlsx
+++ b/BKQBF_TAB-8.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/BK_Compra_Perfeita/CPerfect_Files_GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC2B3CF5-1FCC-4681-9DE1-AA91DC589256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{AC2B3CF5-1FCC-4681-9DE1-AA91DC589256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF7E6464-7984-421B-B21C-7E107DA473E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{53633E7E-D6F2-4DB1-8EFC-B5ACF3C598DF}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="207">
   <si>
     <t>DESCRIÇÃO</t>
   </si>
@@ -560,16 +560,119 @@
   </si>
   <si>
     <t>ATU25AGO</t>
+  </si>
+  <si>
+    <t>7210467</t>
+  </si>
+  <si>
+    <t>COCA COLA LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>7210468</t>
+  </si>
+  <si>
+    <t>COCA COLA LATA DLV BK</t>
+  </si>
+  <si>
+    <t>7210469</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>7210471</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO LATA DLV BK</t>
+  </si>
+  <si>
+    <t>7210472</t>
+  </si>
+  <si>
+    <t>FANTA LARANJA LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>7210473</t>
+  </si>
+  <si>
+    <t>FANTA LARANJA LATA DLV BK</t>
+  </si>
+  <si>
+    <t>7210474</t>
+  </si>
+  <si>
+    <t>GUARANA DIET LATA</t>
+  </si>
+  <si>
+    <t>7210475</t>
+  </si>
+  <si>
+    <t>GUARANA LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>7210476</t>
+  </si>
+  <si>
+    <t>GUARANA LATA DLV BK</t>
+  </si>
+  <si>
+    <t>7210478</t>
+  </si>
+  <si>
+    <t>GUARANA ZERO LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>7210479</t>
+  </si>
+  <si>
+    <t>GUARANA ZERO LATA DLV BK</t>
+  </si>
+  <si>
+    <t>7210480</t>
+  </si>
+  <si>
+    <t>REFRIGERANTE GUARANA LATA</t>
+  </si>
+  <si>
+    <t>9013</t>
+  </si>
+  <si>
+    <t>SPRITE LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>9014</t>
+  </si>
+  <si>
+    <t>SPRITE LATA DLV BK</t>
+  </si>
+  <si>
+    <t>BISCOITO BISCOFF CX C 300UND</t>
+  </si>
+  <si>
+    <t>CARNE FRALDINHA DESF DEFUMADA CX 4KG 4X1</t>
+  </si>
+  <si>
+    <t>COOKIE GRANULADO BAUNI CL CX5X1KG</t>
+  </si>
+  <si>
+    <t>CRUMBS BISCOFF CX C 6KG 8X750G</t>
+  </si>
+  <si>
+    <t>ETIQUETA LACRE DE SEGURANCA DLV C/1000UN</t>
+  </si>
+  <si>
+    <t>PROTEINA SORO DE LEITE CX 12X0,8KG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -589,6 +692,11 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -648,8 +756,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -679,8 +788,9 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Vírgula 2 2" xfId="1" xr:uid="{01DEF522-9E0D-46E0-AC0C-EE4DD12AF6FB}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -700,6 +810,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="CONTAGEM_DIARIA_JUL25"/>
@@ -1314,6 +1425,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Plan_PEDIDO_out24"/>
@@ -1959,6 +2071,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="CONTAGEM_DIARIA_JUL25"/>
@@ -2602,10 +2715,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2925,7 +3034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB15583B-E240-453F-9C06-A311E2614116}">
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M190"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38.5703125" customWidth="1"/>
@@ -9683,6 +9792,237 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C170" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C171" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C172" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C173" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C174" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C175" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C176" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C177" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C178" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C179" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C180" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C181" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C182" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C183" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="2">
+        <v>35219</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C184" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="2">
+        <v>41475</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C185" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="2">
+        <v>42049</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C186" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="2">
+        <v>39059</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C187" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="2">
+        <v>41476</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C188" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="2">
+        <v>37842</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C189" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="2">
+        <v>40442</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C190" s="4">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/BKQBF_TAB-8.xlsx
+++ b/BKQBF_TAB-8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/BK_Compra_Perfeita/CPerfect_Files_GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{AC2B3CF5-1FCC-4681-9DE1-AA91DC589256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF7E6464-7984-421B-B21C-7E107DA473E9}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{AC2B3CF5-1FCC-4681-9DE1-AA91DC589256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA063F6F-26F1-450F-8C58-FCA78F21226E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{53633E7E-D6F2-4DB1-8EFC-B5ACF3C598DF}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="205">
   <si>
     <t>DESCRIÇÃO</t>
   </si>
@@ -634,13 +634,7 @@
     <t>REFRIGERANTE GUARANA LATA</t>
   </si>
   <si>
-    <t>9013</t>
-  </si>
-  <si>
     <t>SPRITE LATA BALCAO BK</t>
-  </si>
-  <si>
-    <t>9014</t>
   </si>
   <si>
     <t>SPRITE LATA DLV BK</t>
@@ -2715,6 +2709,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9793,154 +9791,150 @@
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A170" s="2" t="s">
+      <c r="A170" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C170" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B170" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C170" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A171" s="2" t="s">
+      <c r="B171" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C171" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C172" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B173" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C173" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C174" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A175" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C175" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A176" s="7"/>
+      <c r="B176" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C176" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C177" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B171" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C171" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A172" s="2" t="s">
+      <c r="B178" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C178" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B179" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C179" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B172" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C172" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A173" s="2" t="s">
+      <c r="B180" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C180" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="7"/>
+      <c r="B181" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C181" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C182" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B173" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C173" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A174" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C174" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A175" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C175" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A176" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C176" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C177" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C178" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C179" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C180" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C181" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B182" s="3" t="s">
+      <c r="B183" s="8" t="s">
         <v>198</v>
-      </c>
-      <c r="C182" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="C183" s="4">
         <v>0</v>
@@ -9962,7 +9956,7 @@
         <v>41475</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C185" s="4">
         <v>0</v>
@@ -9973,7 +9967,7 @@
         <v>42049</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C186" s="4">
         <v>0</v>
@@ -9984,7 +9978,7 @@
         <v>39059</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C187" s="4">
         <v>0</v>
@@ -9995,7 +9989,7 @@
         <v>41476</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C188" s="4">
         <v>0</v>
@@ -10006,7 +10000,7 @@
         <v>37842</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C189" s="4">
         <v>0</v>
@@ -10017,7 +10011,7 @@
         <v>40442</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C190" s="4">
         <v>0</v>

--- a/BKQBF_TAB-8.xlsx
+++ b/BKQBF_TAB-8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/BK_Compra_Perfeita/CPerfect_Files_GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{AC2B3CF5-1FCC-4681-9DE1-AA91DC589256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA063F6F-26F1-450F-8C58-FCA78F21226E}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{AC2B3CF5-1FCC-4681-9DE1-AA91DC589256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18B94485-DACB-44CF-AA77-51EE1340CF3C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{53633E7E-D6F2-4DB1-8EFC-B5ACF3C598DF}"/>
   </bookViews>
@@ -9791,7 +9791,7 @@
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A170" s="7" t="s">
+      <c r="A170" s="2" t="s">
         <v>185</v>
       </c>
       <c r="B170" s="8" t="s">
@@ -9802,7 +9802,7 @@
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A171" s="7" t="s">
+      <c r="A171" s="2" t="s">
         <v>173</v>
       </c>
       <c r="B171" s="8" t="s">
@@ -9813,7 +9813,7 @@
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A172" s="7" t="s">
+      <c r="A172" s="2" t="s">
         <v>193</v>
       </c>
       <c r="B172" s="8" t="s">
@@ -9824,7 +9824,7 @@
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A173" s="7" t="s">
+      <c r="A173" s="2" t="s">
         <v>181</v>
       </c>
       <c r="B173" s="8" t="s">
@@ -9835,7 +9835,7 @@
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A174" s="7" t="s">
+      <c r="A174" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B174" s="8" t="s">
@@ -9846,7 +9846,7 @@
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A175" s="7" t="s">
+      <c r="A175" s="2" t="s">
         <v>183</v>
       </c>
       <c r="B175" s="8" t="s">
@@ -9857,7 +9857,7 @@
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A176" s="7"/>
+      <c r="A176" s="2"/>
       <c r="B176" s="8" t="s">
         <v>186</v>
       </c>
@@ -9866,7 +9866,7 @@
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="7" t="s">
+      <c r="A177" s="2" t="s">
         <v>187</v>
       </c>
       <c r="B177" s="8" t="s">
@@ -9877,7 +9877,7 @@
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="7" t="s">
+      <c r="A178" s="2" t="s">
         <v>175</v>
       </c>
       <c r="B178" s="8" t="s">
@@ -9888,7 +9888,7 @@
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="7" t="s">
+      <c r="A179" s="2" t="s">
         <v>189</v>
       </c>
       <c r="B179" s="8" t="s">
@@ -9899,7 +9899,7 @@
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="7" t="s">
+      <c r="A180" s="2" t="s">
         <v>177</v>
       </c>
       <c r="B180" s="8" t="s">
@@ -9910,7 +9910,7 @@
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="7"/>
+      <c r="A181" s="2"/>
       <c r="B181" s="8" t="s">
         <v>196</v>
       </c>
@@ -9919,7 +9919,7 @@
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="7" t="s">
+      <c r="A182" s="2" t="s">
         <v>191</v>
       </c>
       <c r="B182" s="8" t="s">
@@ -9930,7 +9930,7 @@
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="7" t="s">
+      <c r="A183" s="2" t="s">
         <v>179</v>
       </c>
       <c r="B183" s="8" t="s">
